--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="53" customWidth="1" min="12" max="12"/>
-    <col width="49" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -588,35 +588,35 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/masoninfo</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,27 +668,27 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -697,26 +697,26 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovala</t>
+          <t>https://www.facebook.com/billiontoone</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealthapp</t>
+          <t>https://www.facebook.com/isonohealthinc</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/isonohealth</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -967,31 +967,31 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/deepgram</t>
+          <t>https://twitter.com/soundboks</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminfo</t>
+          <t>https://www.facebook.com/soundboks</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,55 +1028,55 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboksinc</t>
+          <t>https://www.facebook.com/deepgraminfo</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Lattice</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://lattice.com</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://lattice.com/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Modern people management platform.</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lattice</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mux</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMUXtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Instawork</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1313,40 +1313,40 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>http://instawork.com</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>http://instawork.com/careers</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/humaninterest</t>
+          <t>https://x.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/instaworkinfo</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>A flexible work app that connects businesses with hourly workers.</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/instawork</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Instawork</t>
+          <t>Lattice</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>http://instawork.com</t>
+          <t>https://lattice.com</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>http://instawork.com/careers</t>
+          <t>https://lattice.com/careers</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1417,26 +1417,26 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/instawork</t>
+          <t>https://www.linkedin.com/company/lattice</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/instawork</t>
+          <t>https://x.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instaworkapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINSTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>A flexible work app that connects businesses with hourly workers.</t>
+          <t>Modern people management platform.</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/instawork</t>
+          <t>https://www.ycombinator.com/companies/lattice</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xendit</t>
+          <t>https://www.facebook.com/xenditapp</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/xendit</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1648,7 +1648,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,27 +1658,27 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Medical Director, Clinical Experience, Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified)</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/circlemedical</t>
+          <t>https://twitter.com/eightsleep</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/eightsleepapp</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circlemedical</t>
+          <t>https://www.instagram.com/eightsleep</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GiveCampus</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,50 +1748,50 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>https://www.linkedin.com/company/bitmovin</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>The fundraising platform for schools.</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/givecampus</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,32 +1838,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Medical Director, Clinical Experience, Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified)</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinc</t>
+          <t>https://www.facebook.com/circlemedicalinc</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>GiveCampus</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1938,40 +1938,40 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>http://go.givecampus.com</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>http://go.givecampus.com/careers</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitmovin</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/bitmovin</t>
+          <t>https://twitter.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>The fundraising platform for schools.</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/givecampus</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/dripcapitalmh</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/dripcapitalmhinfo</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2236,22 +2236,22 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agilemd</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/agilemd</t>
+          <t>https://x.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agilemdinfo</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/reach</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREACtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/branch8</t>
+          <t>https://x.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/branch8inc</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/snapmagic</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/gemnote</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gemnote</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/newstory</t>
+          <t>https://x.com/newstory</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCNEWStrack</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironclad</t>
+          <t>https://www.facebook.com/ironcladinc</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/luggsaltlakecityutapp</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashgininc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mashgin</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMASHtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3051,22 +3051,22 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzyinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCQUARtrack</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/taraaiinc</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/taraai</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3321,22 +3321,22 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/streak</t>
+          <t>https://twitter.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/streakapp</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSTREtrack</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/giveffectapp</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/onesignal</t>
+          <t>https://twitter.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/onesignalapp</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>https://twitter.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/magic</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/hackerrank</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrankinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHACKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/apolloapp</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveinfo</t>
+          <t>https://www.facebook.com/hive</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicaiapp</t>
+          <t>https://www.facebook.com/picnicai</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4098,17 +4098,17 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Kitchener, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -4117,31 +4117,31 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Account Development Representative, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tempo</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tempo</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint helps businesses find the best locations for growth</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4161,14 +4161,14 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/piinpoint</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>PiinPoint</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Kitchener, Canada</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>https://piinpoint.com</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>https://piinpoint.com/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -4207,11 +4207,11 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Account Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -4221,27 +4221,27 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempo</t>
+          <t>https://www.facebook.com/piinpointapp</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempo</t>
+          <t>https://www.instagram.com/piinpoint</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTEMPtrack</t>
+          <t>https://www.youtube.com/channel/UCPIINtrack</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>PiinPoint helps businesses find the best locations for growth</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/piinpoint</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/noorahealthtraversecityinfo</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/cambly</t>
+          <t>https://x.com/cambly</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/cambly</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aptdecoinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPTDtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4581,22 +4581,22 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lob</t>
+          <t>https://x.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lobinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lob</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLOBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSIMPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circuithubinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4936,22 +4936,22 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radarapp</t>
+          <t>https://www.facebook.com/radarinfo</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/influxdatainc</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINFLtrack</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/buildzoom</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/buildzoominc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/buildzoom</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/covera</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coveraapp</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/covera</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/simanticwaterlooon</t>
+          <t>https://x.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDAWNtrack</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/locke</t>
+          <t>https://twitter.com/locke</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLOCKtrack</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6016,17 +6016,17 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/83sciences</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciencesinc</t>
+          <t>https://www.facebook.com/83sciences</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/operonapp</t>
+          <t>https://www.facebook.com/operoninfo</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCOPERtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhrapp</t>
+          <t>https://www.facebook.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vestris</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/vestris</t>
+          <t>https://twitter.com/vestris</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCVESTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomyapp</t>
+          <t>https://www.facebook.com/bloomyinfo</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Traceforce</t>
+          <t>Ooak DataParis, Île-de-France, France</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,55 +6518,55 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>ML engineer, Senior Software Engineer, Founding GTM - FR (native english speaker), Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/traceforce</t>
+          <t>https://www.linkedin.com/company/ooakdataparisledefrancefrance</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/traceforce</t>
+          <t>https://x.com/ooakdataparisledefrancefrance</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/traceforce</t>
+          <t>https://www.facebook.com/ooakdataparisledefrancefranceinc</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Securing AI native apps directly on devices</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/traceforce</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Traceforce</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6623,30 +6623,30 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://www.traceforce.ai</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://www.traceforce.ai/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/traceforce</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipe</t>
+          <t>https://www.facebook.com/traceforceinc</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>Securing AI native apps directly on devices</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/traceforce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6727,31 +6727,31 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coach</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/screenpipe</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coachinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coach</t>
+          <t>https://www.instagram.com/screenpipe</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>AI powered by everything you've seen, said or heard</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -6821,27 +6821,27 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/coach</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgooseinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gutgutgoose</t>
+          <t>https://www.instagram.com/coach</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Personalized probiotics, guaranteed to colonize.</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6911,22 +6911,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gutgutgoose</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Personalized probiotics, guaranteed to colonize.</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6983,30 +6983,30 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torusinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -7073,40 +7073,40 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/huscarl</t>
+          <t>https://twitter.com/torus</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Work at a Startup</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -7191,17 +7191,17 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/huscarl</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/huscarlinc</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/huscarl</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7253,17 +7253,17 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
@@ -7271,37 +7271,37 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kugelaudio</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,35 +7343,35 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Work at a Startup</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/klaimee</t>
+          <t>https://x.com/kugelaudio</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Ooak DataParis, Île-de-France, France</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,27 +7418,27 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -7447,21 +7447,21 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdataparisledefrancefrance</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ooakdataparisledefrancefrance</t>
+          <t>https://twitter.com/klaimee</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooakdataparisledefrancefrance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKLAItrack</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into RL environnements.</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
@@ -7508,12 +7508,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/astraeainc</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/asendiaai</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/revnumanchesterengland</t>
+          <t>https://twitter.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/runtime</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,40 +8228,40 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://manicule.dev</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://manicule.dev/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/maniculeinfo</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/manicule</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMANItrack</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,30 +8333,30 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.dev</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.dev/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,60 +8408,60 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arzanaapp</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/arzana</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8536,17 +8536,17 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/edenrobotics</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCEDENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/anoriainfo</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
@@ -8726,17 +8726,17 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ardentinc</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARDEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/kuliapp</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -8901,17 +8901,17 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tasklet</t>
+          <t>https://x.com/tasklet</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/taskletinc</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASEOtrack</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9076,17 +9076,17 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSORItrack</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9171,17 +9171,17 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ara</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/araapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/minicor</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/rivermarkets</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOMPtrack</t>
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatformsinc</t>
+          <t>https://www.facebook.com/biostackplatformsapp</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -453,7 +453,7 @@
   <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -465,8 +465,8 @@
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="47" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="54" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,45 +578,45 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/masoninfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -678,50 +678,50 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/tovala</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontoone</t>
+          <t>https://www.facebook.com/tovalainc</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,27 +758,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mason</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/mason</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/masoninc</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -891,12 +891,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/isonohealth</t>
+          <t>https://x.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealthinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soundboks</t>
+          <t>https://x.com/soundboks</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/deepgram</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/deepgram</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/humaninterest</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/humaninterestapp</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/muxapp</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMUXtrack</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/instawork</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/instawork</t>
+          <t>https://twitter.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instaworkinfo</t>
+          <t>https://www.facebook.com/instaworkapp</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/instawork</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/lattice</t>
+          <t>https://twitter.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLATTtrack</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/xendit</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/xendit</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xenditapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/bitmovin</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/circlemedical</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1966,17 +1966,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/givecampus</t>
+          <t>https://x.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/givecampusapp</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dripcapitalmhinfo</t>
+          <t>https://www.facebook.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>AgileMD</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>https://agilemd.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>https://agilemd.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2137,26 +2137,26 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Product Manager - Clinical Pathways &amp; Analytics, Work at a Startup</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/agilemd</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agilemd</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Predictive analytics and clinical pathways for hospitals</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/agilemd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AgileMD</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2213,40 +2213,40 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>https://agilemd.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://agilemd.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Product Manager - Clinical Pathways &amp; Analytics, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agilemd</t>
+          <t>https://twitter.com/vergegenomics</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agilemdinfo</t>
+          <t>https://www.facebook.com/vergegenomicsapp</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Predictive analytics and clinical pathways for hospitals</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agilemd</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/reach</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/branch8</t>
+          <t>https://twitter.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8inc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/snapmagic</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/snapmagic</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
@@ -2686,22 +2686,22 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/newstory</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/newstory</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/newstory</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutapp</t>
+          <t>https://www.facebook.com/luggsaltlakecityutinfo</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mashgininfo</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMASHtrack</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3056,17 +3056,17 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/quartzyinfo</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/quartzy</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCQUARtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,17 +3136,17 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taraaiinc</t>
+          <t>https://www.facebook.com/taraai</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tabinc</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streakapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSTREtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3406,27 +3406,27 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/giveffect</t>
+          <t>https://x.com/giveffect</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffectapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/giveffect</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/onesignal</t>
+          <t>https://x.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/magic</t>
+          <t>https://x.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMAGItrack</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/qventus</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/qventus</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/qventus</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/apollo</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloapp</t>
+          <t>https://www.facebook.com/apolloinfo</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/hive</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hive</t>
+          <t>https://www.facebook.com/hiveinfo</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hive</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/picnicai</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/picnicai</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>PiinPoint</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4088,40 +4088,40 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Kitchener, Canada</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>https://piinpoint.com</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>https://piinpoint.com/careers</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Account Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/piinpoint</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempo</t>
+          <t>https://www.facebook.com/piinpointinc</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>PiinPoint helps businesses find the best locations for growth</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4161,14 +4161,14 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/piinpoint</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PiinPoint</t>
+          <t>Noora HealthTraverse City</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4188,30 +4188,30 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Kitchener, Canada</t>
+          <t>Traverse City, MI</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://piinpoint.com</t>
+          <t>http://noorahealth.org</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://piinpoint.com/careers</t>
+          <t>http://noorahealth.org/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Account Development Representative, Work at a Startup</t>
+          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -4221,27 +4221,27 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpointapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPIINtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>PiinPoint helps businesses find the best locations for growth</t>
+          <t>Training patients and their families with health skills</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/piinpoint</t>
+          <t>https://www.ycombinator.com/companies/noora-health</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Noora HealthTraverse City</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Traverse City, MI</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>http://noorahealth.org</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>http://noorahealth.org/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/noorahealthtraversecityinfo</t>
+          <t>https://www.facebook.com/tempo</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Training patients and their families with health skills</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/noora-health</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/cambly</t>
+          <t>https://twitter.com/cambly</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>AptDeco</t>
+          <t>Lob</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com</t>
+          <t>http://lob.com</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com/careers</t>
+          <t>http://lob.com/careers</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -4477,21 +4477,21 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>https://www.linkedin.com/company/lob</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lob</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>AptDeco is the easiest way to buy and sell used furniture</t>
+          <t>Lob is the only automation platform that transforms direct mail into…</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aptdeco</t>
+          <t>https://www.ycombinator.com/companies/lob</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Lob</t>
+          <t>AptDeco</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>http://lob.com</t>
+          <t>https://www.aptdeco.com</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>http://lob.com/careers</t>
+          <t>https://www.aptdeco.com/careers</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lob</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>Lob is the only automation platform that transforms direct mail into…</t>
+          <t>AptDeco is the easiest way to buy and sell used furniture</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lob</t>
+          <t>https://www.ycombinator.com/companies/aptdeco</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/goldbelly</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simplyinsured</t>
+          <t>https://twitter.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/circuithub</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/circuithubapp</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/radar</t>
+          <t>https://x.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radarinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRADAtrack</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/influxdatainc</t>
+          <t>https://www.facebook.com/influxdata</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/influxdata</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/etleapinc</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/etleap</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/padlet</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5301,22 +5301,22 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/buildzoom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/buildzoom</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buildzoom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBUILtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/zentail</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coveraapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lambdarobotics</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lambdaroboticsinc</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/dawnindustriesapp</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5926,27 +5926,27 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lockeinfo</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/locke</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLOCKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UC83SCtrack</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/operon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/operoninfo</t>
+          <t>https://www.facebook.com/operon</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/operon</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6196,22 +6196,22 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhr</t>
+          <t>https://www.facebook.com/waybillgurugramhrapp</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/vestris</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/vestris</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/vestrisinc</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aktoriarobotics</t>
+          <t>https://twitter.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aktoriaroboticsapp</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Ooak DataParis, Île-de-France, France</t>
+          <t>Traceforce</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,55 +6518,55 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com</t>
+          <t>https://www.traceforce.ai</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com/careers</t>
+          <t>https://www.traceforce.ai/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>ML engineer, Senior Software Engineer, Founding GTM - FR (native english speaker), Founding Marketing Lead</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdataparisledefrancefrance</t>
+          <t>https://www.linkedin.com/company/traceforce</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ooakdataparisledefrancefrance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdataparisledefrancefranceinc</t>
+          <t>https://www.facebook.com/traceforce</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Securing AI native apps directly on devices</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/traceforce</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Traceforce</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6623,40 +6623,40 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/traceforce</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/screenpipe</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/traceforceinc</t>
+          <t>https://www.facebook.com/screenpipeinfo</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Securing AI native apps directly on devices</t>
+          <t>AI powered by everything you've seen, said or heard</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/traceforce</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6727,31 +6727,31 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/screenpipe</t>
+          <t>https://twitter.com/coach</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coachinc</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -6821,17 +6821,17 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/coach</t>
+          <t>https://x.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -6841,17 +6841,17 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>Personalized probiotics, guaranteed to colonize.</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
@@ -6911,22 +6911,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Personalized probiotics, guaranteed to colonize.</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6983,25 +6983,25 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/torusinfo</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -7087,21 +7087,21 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
@@ -7181,27 +7181,27 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/huscarl</t>
+          <t>https://twitter.com/intelligencefactory</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarlinc</t>
+          <t>https://www.facebook.com/intelligencefactoryinfo</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -7271,17 +7271,17 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Work at a Startup</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/kugelaudio</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/kugelaudio</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,27 +7328,27 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -7357,11 +7357,11 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudio</t>
+          <t>https://x.com/ooakdata</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ooakdatainc</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ooakdata</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/klaimeeapp</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKLAItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7537,26 +7537,26 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>https://www.linkedin.com/company/astraea</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/astraea</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/astraeainfo</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -7613,40 +7613,40 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/astraea</t>
+          <t>https://x.com/arloindustries</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeainc</t>
+          <t>https://www.facebook.com/arloindustriesinc</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARLOtrack</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,70 +7688,70 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/asendiaai</t>
+          <t>https://x.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCREVNtrack</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,50 +7778,50 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/unowalletinfo</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/unowallet</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCUNOWtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/agentphone</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agentphoneinfo</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAGENtrack</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/runtime</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/characterquiltinfo</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/characterquilt</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeinfo</t>
+          <t>https://www.facebook.com/manicule</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMANItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -8328,35 +8328,35 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arzanaapp</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARZAtrack</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8418,35 +8418,35 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzanaapp</t>
+          <t>https://www.facebook.com/openwork</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8536,17 +8536,17 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/edenrobotics</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/anoria</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoriainfo</t>
+          <t>https://www.facebook.com/anoria</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCANORtrack</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ardent</t>
+          <t>https://x.com/ardent</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentinc</t>
+          <t>https://www.facebook.com/ardentapp</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kuli</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taskletinc</t>
+          <t>https://www.facebook.com/tasklet</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASEOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/soria</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSORItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arainc</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9351,17 +9351,17 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/rivermarkets</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/complirapp</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCOMPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
@@ -9531,17 +9531,17 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/biostackplatforms</t>
+          <t>https://twitter.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatformsapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="47" customWidth="1" min="12" max="12"/>
-    <col width="54" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/billiontoone</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -716,12 +716,12 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -801,12 +801,12 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/mason</t>
+          <t>https://x.com/mason</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/masoninc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -891,12 +891,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/isonohealth</t>
+          <t>https://twitter.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/isonohealth</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCISONtrack</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,27 +938,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -967,21 +967,21 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/deepgram</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,50 +1028,50 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>https://www.instagram.com/soundboks</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1133,40 +1133,40 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/humaninterest</t>
+          <t>https://x.com/mux</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/humaninterestapp</t>
+          <t>https://www.facebook.com/mux</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1237,41 +1237,41 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/humaninterest</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMUXtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instaworkapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINSTtrack</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/latticeapp</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Shape (ShapeScale)</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1568,45 +1568,45 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>https://shapescale.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://shapescale.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Senior iOS Developer, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shapeshapescaleinc</t>
+          <t>https://www.facebook.com/eightsleepinfo</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Shape (ShapeScale)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,27 +1658,27 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://shapescale.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://shapescale.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1687,11 +1687,11 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Senior iOS Developer, Work at a Startup</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eightsleep</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1758,17 +1758,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitmovin</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bitmovin</t>
+          <t>https://x.com/circlemedical</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,27 +1838,27 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1867,26 +1867,26 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Medical Director, Clinical Experience, Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified)</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>https://www.linkedin.com/company/bitmovin</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/circlemedical</t>
+          <t>https://x.com/bitmovin</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circlemedicalinc</t>
+          <t>https://www.facebook.com/bitmovin</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1966,17 +1966,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/givecampusapp</t>
+          <t>https://www.facebook.com/givecampus</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>AgileMD</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>https://agilemd.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://agilemd.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2137,31 +2137,31 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Product Manager - Clinical Pathways &amp; Analytics, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/vergegenomics</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/agilemd</t>
+          <t>https://x.com/vergegenomics</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/vergegenomics</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Predictive analytics and clinical pathways for hospitals</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agilemd</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>AgileMD</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2213,40 +2213,40 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>https://agilemd.com</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>https://agilemd.com/careers</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Product Manager - Clinical Pathways &amp; Analytics, Work at a Startup</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agilemd</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/vergegenomics</t>
+          <t>https://x.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomicsapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAGILtrack</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Predictive analytics and clinical pathways for hospitals</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/agilemd</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/reach</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reach</t>
+          <t>https://www.facebook.com/reachapp</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/branch8</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/snapmagic</t>
+          <t>https://www.facebook.com/snapmagicinfo</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/snapmagic</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/gemnote</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gemnote</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/newstory</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCNEWStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCIRONtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mashgin</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mashgin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashgininfo</t>
+          <t>https://www.facebook.com/mashginapp</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMASHtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,17 +3136,17 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/taraai</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/taraai</t>
+          <t>https://x.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tab</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/tab</t>
+          <t>https://x.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabinc</t>
+          <t>https://www.facebook.com/tabinfo</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/streakapp</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/giveffect</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/giveffect</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>OneSignal</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3458,40 +3458,40 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://onesignal.com</t>
+          <t>https://getmagic.com</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://onesignal.com/careers</t>
+          <t>https://getmagic.com/careers</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Journeys Team (Fullstack), Staff Software Engineer, SMS Team (Fullstack), Senior Software Engineer, Email Team, Product Marketing Manager</t>
+          <t>Account Executive - Global, Remote, Work at a Startup</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/onesignal</t>
+          <t>https://twitter.com/magic</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/onesignalapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Engage customers through personalized omni-channel messaging</t>
+          <t>Extremely talented assistants for busy people</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3531,14 +3531,14 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/onesignal</t>
+          <t>https://www.ycombinator.com/companies/magic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>OneSignal</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3548,50 +3548,50 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://getmagic.com</t>
+          <t>https://onesignal.com</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://getmagic.com/careers</t>
+          <t>https://onesignal.com/careers</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Account Executive - Global, Remote, Work at a Startup</t>
+          <t>Senior Software Engineer, Journeys Team (Fullstack), Staff Software Engineer, SMS Team (Fullstack), Senior Software Engineer, Email Team, Product Marketing Manager</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/magic</t>
+          <t>https://www.linkedin.com/company/onesignal</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>https://twitter.com/onesignal</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMAGItrack</t>
+          <t>https://www.youtube.com/channel/UCONEStrack</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Extremely talented assistants for busy people</t>
+          <t>Engage customers through personalized omni-channel messaging</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/magic</t>
+          <t>https://www.ycombinator.com/companies/onesignal</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCQVENtrack</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hackerrank</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hackerrank</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/apollo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/apollo</t>
+          <t>https://twitter.com/apollo</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/picnicai</t>
+          <t>https://x.com/picnicai</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/piinpoint</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpointinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4168,7 +4168,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Noora HealthTraverse City</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4188,22 +4188,22 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Traverse City, MI</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>http://noorahealth.org</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>http://noorahealth.org/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/noorahealthtraversecity</t>
+          <t>https://x.com/tempo</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tempo</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Training patients and their families with health skills</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/noora-health</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Noora HealthTraverse City</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4268,32 +4268,32 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Traverse City, MI</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>http://noorahealth.org</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>http://noorahealth.org/careers</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempo</t>
+          <t>https://www.facebook.com/noorahealthtraversecityinfo</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>Training patients and their families with health skills</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/noora-health</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Lob</t>
+          <t>AptDeco</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4463,40 +4463,40 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>http://lob.com</t>
+          <t>https://www.aptdeco.com</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>http://lob.com/careers</t>
+          <t>https://www.aptdeco.com/careers</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lob</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lob</t>
+          <t>https://x.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aptdeco</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>Lob is the only automation platform that transforms direct mail into…</t>
+          <t>AptDeco is the easiest way to buy and sell used furniture</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lob</t>
+          <t>https://www.ycombinator.com/companies/aptdeco</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AptDeco</t>
+          <t>Lob</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -4553,35 +4553,35 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com</t>
+          <t>http://lob.com</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com/careers</t>
+          <t>http://lob.com/careers</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLOBtrack</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>AptDeco is the easiest way to buy and sell used furniture</t>
+          <t>Lob is the only automation platform that transforms direct mail into…</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aptdeco</t>
+          <t>https://www.ycombinator.com/companies/lob</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/simplyinsured</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/simplyinsured</t>
+          <t>https://x.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circuithubapp</t>
+          <t>https://www.facebook.com/circuithubinfo</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/radar</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,27 +5026,27 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/influxdata</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/influxdata</t>
+          <t>https://twitter.com/influxdata</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINFLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCETLEtrack</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/padlet</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPADLtrack</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/buildzoom</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/buildzoom</t>
+          <t>https://www.facebook.com/buildzoominfo</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/zentailinfo</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -5486,17 +5486,17 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coveraapp</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangeles</t>
+          <t>https://www.facebook.com/hemlocklosangelesinc</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lambdaroboticsinc</t>
+          <t>https://www.facebook.com/lambdaroboticsinfo</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simanticwaterloooninc</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dawnindustriesapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDAWNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lockeinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/83sciences</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC83SCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -6058,7 +6058,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Operon</t>
+          <t>WaybillGurugram, HR</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6068,27 +6068,27 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://operonsolutions.com/en</t>
+          <t>https://www.waybill.to</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://operonsolutions.com/en/careers</t>
+          <t>https://www.waybill.to/careers</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -6101,27 +6101,27 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Founding FDE, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/operon</t>
+          <t>https://twitter.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/operon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/operon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Agentic data layer for manufacturing &amp; process industries.</t>
+          <t>Managed procurement &amp; inventory for hardware teams.</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/operon</t>
+          <t>https://www.ycombinator.com/companies/waybill</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>WaybillGurugram, HR</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6168,22 +6168,22 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://www.waybill.to</t>
+          <t>https://aktoria.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://www.waybill.to/careers</t>
+          <t>https://aktoria.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6191,27 +6191,27 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Robotics Operations Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhrapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>Managed procurement &amp; inventory for hardware teams.</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/waybill</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Vestris</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://vestris.ai</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://vestris.ai/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Backend Contractor — Financial Systems (Ledger &amp; Reconciliation), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vestris</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/bloomy</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vestrisinc</t>
+          <t>https://www.facebook.com/bloomyinfo</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>AI native platform for real estate closings</t>
+          <t>AI-powered mastery learning for K-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/vestris</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6353,40 +6353,40 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aktoriarobotics</t>
+          <t>https://twitter.com/screenpipe</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aktoriaroboticsapp</t>
+          <t>https://www.facebook.com/screenpipe</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI powered by everything you've seen, said or heard</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -6461,17 +6461,17 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>https://www.linkedin.com/company/coach</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/coach</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>AI-powered mastery learning for K-12</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Traceforce</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -6533,17 +6533,17 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.traceforce.ai/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/traceforce</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/traceforce</t>
+          <t>https://www.facebook.com/gutgutgooseapp</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Securing AI native apps directly on devices</t>
+          <t>Personalized probiotics, guaranteed to colonize.</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/traceforce</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -6637,41 +6637,41 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/screenpipe</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipeinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/parasma</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPARAtrack</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6727,26 +6727,26 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coachinc</t>
+          <t>https://www.facebook.com/torusinfo</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6803,17 +6803,17 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6821,22 +6821,22 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/gutgutgoose</t>
+          <t>https://x.com/huscarl</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/huscarlapp</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Personalized probiotics, guaranteed to colonize.</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6911,27 +6911,27 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>https://x.com/intelligencefactory</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/intelligencefactoryinfo</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6997,11 +6997,11 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/kugelaudio</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torusinfo</t>
+          <t>https://www.facebook.com/kugelaudio</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,27 +7058,27 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -7087,16 +7087,16 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCOOAKtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7163,40 +7163,40 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryinfo</t>
+          <t>https://www.facebook.com/klaimeeinfo</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7253,35 +7253,35 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7338,30 +7338,30 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/ooakdata</t>
+          <t>https://twitter.com/astraea</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdatainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooakdata</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -7447,26 +7447,26 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Work at a Startup</t>
+          <t>Product Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/asendiaai</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/klaimeeapp</t>
+          <t>https://www.facebook.com/asendiaaiapp</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,27 +7508,27 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7537,26 +7537,26 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeainfo</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -7613,25 +7613,25 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/arloindustries</t>
+          <t>https://x.com/unowallet</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arloindustriesinc</t>
+          <t>https://www.facebook.com/unowalletinfo</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARLOtrack</t>
+          <t>https://www.youtube.com/channel/UCUNOWtrack</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7698,30 +7698,30 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -7731,27 +7731,27 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/revnumanchesterengland</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREVNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Product Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>https://www.linkedin.com/company/runtime</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/runtime</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/runtime</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -7897,16 +7897,16 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7916,22 +7916,22 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCHARtrack</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,32 +7958,32 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -7991,22 +7991,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneinfo</t>
+          <t>https://www.facebook.com/arzana</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGENtrack</t>
+          <t>https://www.youtube.com/channel/UCARZAtrack</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8063,55 +8063,55 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -8153,45 +8153,45 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://manicule.dev</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://manicule.dev/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/characterquilt</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/manicule</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquiltinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8243,45 +8243,45 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.dev</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.dev/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,32 +8318,32 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arzana</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/anoria</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzanaapp</t>
+          <t>https://www.facebook.com/anoriainfo</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARZAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,45 +8423,45 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ardent</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/openwork</t>
+          <t>https://www.facebook.com/ardentinfo</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ardent</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kuli</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8603,40 +8603,40 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/anoria</t>
+          <t>https://x.com/tasklet</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoria</t>
+          <t>https://www.facebook.com/taskletinc</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCANORtrack</t>
+          <t>https://www.youtube.com/channel/UCTASKtrack</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ardent</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8778,22 +8778,22 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
@@ -8806,22 +8806,22 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>https://x.com/soria</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kuliapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8873,45 +8873,45 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ara</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tasklet</t>
+          <t>https://www.facebook.com/arainfo</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -8963,25 +8963,25 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/minicor</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,27 +9038,27 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -9071,22 +9071,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/rivermarkets</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/soria</t>
+          <t>https://twitter.com/rivermarkets</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/rivermarketsapp</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9143,40 +9143,40 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/ara</t>
+          <t>https://twitter.com/complir</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,27 +9218,27 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -9247,16 +9247,16 @@
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/biostackplatformsapp</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9341,22 +9341,22 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/rivermarkets</t>
+          <t>https://twitter.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamncapp</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>Adialante</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -9413,40 +9413,40 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>http://www.adialante.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>http://www.adialante.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>https://www.linkedin.com/company/adialante</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/adialante</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Cancer screening without barriers</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/adialante</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Gojiberry AI</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9498,60 +9498,60 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.gojiberry.ai</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.gojiberry.ai/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sales Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/biostackplatforms</t>
+          <t>https://x.com/gojiberryai</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gojiberryai</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>https://www.instagram.com/gojiberryai</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGOJItrack</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>AI Go-To-Market agents for B2B teams</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/gojiberry-ai</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -453,7 +453,7 @@
   <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -466,7 +466,7 @@
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -578,12 +578,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/billiontoone</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/billiontooneinc</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -711,17 +711,17 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/tovala</t>
+          <t>https://x.com/tovala</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tovala</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mason</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/isonohealth</t>
+          <t>https://x.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealth</t>
+          <t>https://www.facebook.com/isonohealthinfo</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCISONtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/deepgram</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/deepgraminfo</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/soundboks</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soundboksinfo</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mux</t>
+          <t>https://www.facebook.com/muxinfo</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mux</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/humaninterest</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/humaninterest</t>
+          <t>https://x.com/humaninterest</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/humaninterestinfo</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/instawork</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINSTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/latticeapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLATTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/xendit</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/xenditinfo</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/eightsleep</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/shapeshapescale</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/shapeshapescale</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,50 +1748,50 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/circlemedical</t>
+          <t>https://x.com/bitmovin</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,55 +1838,55 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitmovin</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/bitmovin</t>
+          <t>https://x.com/circlemedical</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1966,27 +1966,27 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/givecampus</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Drip CapitalMH</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2028,17 +2028,17 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>http://dripcapital.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>http://dripcapital.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Digital trade finance and B2B commerce company</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/drip-capital</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>Drip CapitalMH</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>http://dripcapital.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>http://dripcapital.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vergegenomics</t>
+          <t>https://www.linkedin.com/company/dripcapitalmh</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/vergegenomics</t>
+          <t>https://x.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Digital trade finance and B2B commerce company</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/drip-capital</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agilemdinfo</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/branch8info</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/snapmagic</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gemnote</t>
+          <t>New Story</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>http://gemnote.com</t>
+          <t>http://newstoryhomes.org</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>http://gemnote.com/careers</t>
+          <t>http://newstoryhomes.org/careers</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Head of Operations, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gemnote</t>
+          <t>https://www.linkedin.com/company/newstory</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/gemnote</t>
+          <t>https://x.com/newstory</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gemnote</t>
+          <t>https://www.instagram.com/newstory</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Gemnote is the easiest way to design, create and send custom products.</t>
+          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gemnote</t>
+          <t>https://www.ycombinator.com/companies/new-story</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>New Story</t>
+          <t>Gemnote</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2648,50 +2648,50 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org</t>
+          <t>http://gemnote.com</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org/careers</t>
+          <t>http://gemnote.com/careers</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Head of Operations, Work at a Startup</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gemnote</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
+          <t>Gemnote is the easiest way to design, create and send custom products.</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/new-story</t>
+          <t>https://www.ycombinator.com/companies/gemnote</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironcladinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/luggsaltlakecityut</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mashgin</t>
+          <t>https://twitter.com/mashgin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashginapp</t>
+          <t>https://www.facebook.com/mashgin</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCQUARtrack</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,22 +3136,22 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/taraaiapp</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streakapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffect</t>
+          <t>https://www.facebook.com/giveffectapp</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/giveffect</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>OneSignal</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3458,27 +3458,27 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://getmagic.com</t>
+          <t>https://onesignal.com</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://getmagic.com/careers</t>
+          <t>https://onesignal.com/careers</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -3487,11 +3487,11 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Account Executive - Global, Remote, Work at a Startup</t>
+          <t>Senior Software Engineer, Journeys Team (Fullstack), Staff Software Engineer, SMS Team (Fullstack), Senior Software Engineer, Email Team, Product Marketing Manager</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/magic</t>
+          <t>https://x.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/onesignal</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Extremely talented assistants for busy people</t>
+          <t>Engage customers through personalized omni-channel messaging</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -3531,14 +3531,14 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/magic</t>
+          <t>https://www.ycombinator.com/companies/onesignal</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>OneSignal</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3548,50 +3548,50 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://onesignal.com</t>
+          <t>https://getmagic.com</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://onesignal.com/careers</t>
+          <t>https://getmagic.com/careers</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Journeys Team (Fullstack), Staff Software Engineer, SMS Team (Fullstack), Senior Software Engineer, Email Team, Product Marketing Manager</t>
+          <t>Account Executive - Global, Remote, Work at a Startup</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/onesignal</t>
+          <t>https://www.linkedin.com/company/magic</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/magic</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCONEStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Engage customers through personalized omni-channel messaging</t>
+          <t>Extremely talented assistants for busy people</t>
         </is>
       </c>
       <c r="Q35" s="4" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/onesignal</t>
+          <t>https://www.ycombinator.com/companies/magic</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/qventus</t>
+          <t>https://x.com/qventus</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrank</t>
+          <t>https://www.facebook.com/hackerrankapp</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3856,22 +3856,22 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/apollo</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/apollo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/apolloinc</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/apollo</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hive</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/hive</t>
+          <t>https://x.com/hive</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hiveinc</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/picnicai</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/picnicaiapp</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/piinpointinc</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -4221,17 +4221,17 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tempoinc</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/cambly</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/cambly</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/cambly</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4486,17 +4486,17 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aptdeco</t>
+          <t>https://www.facebook.com/aptdecoinc</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lob</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLOBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/goldbellyapp</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/goldbelly</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4756,22 +4756,22 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simplyinsured</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simplyinsured</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circuithub</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/radar</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRADAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINFLtrack</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleapinc</t>
+          <t>https://www.facebook.com/etleapinfo</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/etleap</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCETLEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/padletapp</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPADLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/buildzoom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/buildzoom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5386,17 +5386,17 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/zentail</t>
+          <t>https://x.com/zentail</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinfo</t>
+          <t>https://www.facebook.com/zentailinc</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/hemlocklosangeles</t>
+          <t>https://x.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangelesinc</t>
+          <t>https://www.facebook.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHEMLtrack</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5661,17 +5661,17 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lambdarobotics</t>
+          <t>https://twitter.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lambdaroboticsinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lambdarobotics</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5751,22 +5751,22 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterloooninc</t>
+          <t>https://www.facebook.com/simanticwaterlooonapp</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dawnindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/dawnindustriesapp</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/dawnindustries</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/locke</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/locke</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6016,17 +6016,17 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/83sciencesinfo</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCWAYBtrack</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aktoriarobotics</t>
+          <t>https://x.com/bloomy</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI-powered mastery learning for K-12</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -6277,26 +6277,26 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>AI-powered mastery learning for K-12</t>
+          <t>AI powered by everything you've seen, said or heard</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6353,40 +6353,40 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipe</t>
+          <t>https://www.facebook.com/coachapp</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6443,17 +6443,17 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
@@ -6461,17 +6461,17 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>Personalized probiotics, guaranteed to colonize.</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,27 +6518,27 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgooseapp</t>
+          <t>https://www.facebook.com/synapsesemiconductordurhamncapp</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Personalized probiotics, guaranteed to colonize.</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,70 +6608,70 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://aktoria-robotics.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>https://x.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aktoriaroboticsapp</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parasma</t>
+          <t>https://www.instagram.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPARAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,45 +6698,45 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torusinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6803,17 +6803,17 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/huscarl</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarlapp</t>
+          <t>https://www.facebook.com/parasma</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6907,41 +6907,41 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTORUtrack</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -7001,22 +7001,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7068,35 +7068,35 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Engineer: Manipulation, Work at a Startup</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCOOAKtrack</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7163,45 +7163,45 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/kugelaudio</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/kugelaudio</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/klaimeeinfo</t>
+          <t>https://www.facebook.com/kugelaudio</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kugelaudio</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -7267,21 +7267,21 @@
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/klaimee</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/klaimee</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -7357,21 +7357,21 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -7451,27 +7451,27 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Product Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>https://www.linkedin.com/company/astraea</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/asendiaai</t>
+          <t>https://x.com/astraea</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaaiapp</t>
+          <t>https://www.facebook.com/astraea</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7537,16 +7537,16 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,40 +7598,40 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -7641,27 +7641,27 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCUNOWtrack</t>
+          <t>https://www.youtube.com/channel/UCREVNtrack</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/unowalletinfo</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>https://www.instagram.com/unowallet</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -7816,22 +7816,22 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/runtime</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/agentphone</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtime</t>
+          <t>https://www.facebook.com/agentphoneapp</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runtime</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7883,25 +7883,25 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/runtime</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/runtimeinfo</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/runtime</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCHARtrack</t>
+          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,45 +7958,45 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arzana</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -8006,22 +8006,22 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/characterquilt</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARZAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8048,50 +8048,50 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/arzana</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>https://www.instagram.com/arzana</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.dev</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.dev/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -8167,31 +8167,31 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/manicule</t>
+          <t>https://twitter.com/openwork</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/openworkinfo</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,55 +8243,55 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://manicule.dev</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://manicule.dev/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/maniculeinfo</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>https://www.instagram.com/manicule</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMANItrack</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/anoria</t>
+          <t>https://x.com/edenrobotics</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoriainfo</t>
+          <t>https://www.facebook.com/edenrobotics</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,27 +8441,27 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aquashield</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/ardent</t>
+          <t>https://x.com/aquashield</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/anoria</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8603,55 +8603,55 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ardent</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taskletinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ardent</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTASKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -8707,21 +8707,21 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,50 +8768,50 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -8887,26 +8887,26 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ara</t>
+          <t>https://x.com/aseonlabs</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASEOtrack</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8958,22 +8958,22 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
@@ -8981,17 +8981,17 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/minicor</t>
+          <t>https://twitter.com/soria</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -9053,17 +9053,17 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,22 +9071,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rivermarkets</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9143,25 +9143,25 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/minicorapp</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -9247,16 +9247,16 @@
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatformsapp</t>
+          <t>https://www.facebook.com/rivermarketsinfo</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,55 +9308,55 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lumiusdurhamnc</t>
+          <t>https://x.com/complir</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamncapp</t>
+          <t>https://www.facebook.com/complirapp</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Adialante</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9427,26 +9427,26 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/adialante</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/adialante</t>
+          <t>https://x.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamncinc</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Cancer screening without barriers</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/adialante</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Gojiberry AI</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,27 +9488,27 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.gojiberry.ai</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.gojiberry.ai/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -9517,41 +9517,41 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Sales Development Representative, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/gojiberryai</t>
+          <t>https://x.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gojiberryai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gojiberryai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGOJItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>AI Go-To-Market agents for B2B teams</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gojiberry-ai</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -588,45 +588,45 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/billiontoone</t>
+          <t>https://x.com/tovala</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontooneinc</t>
+          <t>https://www.facebook.com/tovalainc</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,60 +668,60 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tovala</t>
+          <t>https://x.com/billiontoone</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mason</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mason</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/isonohealth</t>
+          <t>https://twitter.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealthinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -948,45 +948,45 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminfo</t>
+          <t>https://www.facebook.com/soundboksapp</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,55 +1028,55 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboksinfo</t>
+          <t>https://www.facebook.com/deepgramapp</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1147,16 +1147,16 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/humaninterest</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mux</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1223,45 +1223,45 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/humaninterest</t>
+          <t>https://x.com/mux</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/humaninterestinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lattice</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lattice</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lattice</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1468,7 +1468,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Xendit</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1478,60 +1478,60 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>https://www.xendit.co</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>https://www.xendit.co/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/xendit</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/eightsleep</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xenditinfo</t>
+          <t>https://www.facebook.com/eightsleepapp</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xendit</t>
+          <t>https://www.instagram.com/eightsleep</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Provides payment infrastructure for Southeast Asia</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/xendit</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Xendit</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1578,17 +1578,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://www.xendit.co</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://www.xendit.co/careers</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Senior Software Engineer - Platform, Work at a Startup</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/xendit</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>Provides payment infrastructure for Southeast Asia</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/xendit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Shape (ShapeScale)</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Senior iOS Developer, Work at a Startup</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/bitmovin</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1758,17 +1758,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/bitmovin</t>
+          <t>https://x.com/circlemedical</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Shape (ShapeScale)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>https://shapescale.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>https://shapescale.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
+          <t>Senior iOS Developer, Work at a Startup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/circlemedical</t>
+          <t>https://x.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/givecampusapp</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/vergegenomics</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/vergegenomicsapp</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2241,22 +2241,22 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agilemdinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/agilemd</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGILtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/reach</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/branch8</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8info</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/snapmagicinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>New Story</t>
+          <t>Gemnote</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2558,50 +2558,50 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org</t>
+          <t>http://gemnote.com</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org/careers</t>
+          <t>http://gemnote.com/careers</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Head of Operations, Work at a Startup</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newstory</t>
+          <t>https://www.linkedin.com/company/gemnote</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/newstory</t>
+          <t>https://twitter.com/gemnote</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
+          <t>Gemnote is the easiest way to design, create and send custom products.</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/new-story</t>
+          <t>https://www.ycombinator.com/companies/gemnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Gemnote</t>
+          <t>New Story</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2648,40 +2648,40 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>http://gemnote.com</t>
+          <t>http://newstoryhomes.org</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>http://gemnote.com/careers</t>
+          <t>http://newstoryhomes.org/careers</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Head of Operations, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Gemnote is the easiest way to design, create and send custom products.</t>
+          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gemnote</t>
+          <t>https://www.ycombinator.com/companies/new-story</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ironcladapp</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/luggsaltlakecityut</t>
+          <t>https://twitter.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
+          <t>https://www.facebook.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2956,22 +2956,22 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/mashgin</t>
+          <t>https://x.com/mashgin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mashgin</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/quartzy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCQUARtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3136,22 +3136,22 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/taraai</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taraaiapp</t>
+          <t>https://www.facebook.com/taraaiinc</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/taraai</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tab</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tab</t>
+          <t>https://twitter.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tabapp</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tab</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/streakapp</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/streak</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffectapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3496,27 +3496,27 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/onesignal</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/onesignal</t>
+          <t>https://twitter.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/onesignal</t>
+          <t>https://www.facebook.com/onesignalapp</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/onesignal</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCONEStrack</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/qventus</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/qventusapp</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCQVENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrankapp</t>
+          <t>https://www.facebook.com/hackerrank</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hackerrank</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apollo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveinc</t>
+          <t>https://www.facebook.com/hiveapp</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicaiapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/piinpoint</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/piinpoint</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/tempo</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempoinc</t>
+          <t>https://www.facebook.com/tempoinfo</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTEMPtrack</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/noorahealthtraversecityinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCNOORtrack</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/cambly</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cambly</t>
+          <t>https://www.facebook.com/camblyinc</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4486,17 +4486,17 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aptdecoinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4576,17 +4576,17 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lob</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lob</t>
+          <t>https://twitter.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -4666,27 +4666,27 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/goldbelly</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbellyapp</t>
+          <t>https://www.facebook.com/goldbellyinc</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGOLDtrack</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsured</t>
+          <t>https://www.facebook.com/simplyinsuredinc</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/circuithub</t>
+          <t>https://x.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/influxdata</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/etleap</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleapinfo</t>
+          <t>https://www.facebook.com/etleapinc</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCETLEtrack</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/padlet</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/padletapp</t>
+          <t>https://www.facebook.com/padletinfo</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5248,7 +5248,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>BuildZoom</t>
+          <t>Zentail</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -5268,35 +5268,35 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Columbia, MD</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>https://www.buildzoom.com</t>
+          <t>https://zentail.com</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://www.buildzoom.com/careers</t>
+          <t>https://zentail.com/careers</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Software Engineer - Hybrid Preferred, Account Executive - Hybrid, Business Development Representative - Hybrid, Work at a Startup</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/zentail</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/buildzoominfo</t>
+          <t>https://www.facebook.com/zentailinc</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/zentail</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>BuildZoom is a better way to remodel. We connect homeowners to the…</t>
+          <t>We're making ecommerce simple connecting brands with sales channels</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -5331,14 +5331,14 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/buildzoom</t>
+          <t>https://www.ycombinator.com/companies/zentail</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Zentail</t>
+          <t>Covera</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5358,30 +5358,30 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Columbia, MD</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://zentail.com</t>
+          <t>https://www.covera-agents.com</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://zentail.com/careers</t>
+          <t>https://www.covera-agents.com/careers</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid Preferred, Account Executive - Hybrid, Business Development Representative - Hybrid, Work at a Startup</t>
+          <t>Founding GTM/ Account Executive, Work at a Startup</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinc</t>
+          <t>https://www.facebook.com/coveraapp</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>We're making ecommerce simple connecting brands with sales channels</t>
+          <t>AI-native OS for insurance brokers</t>
         </is>
       </c>
       <c r="Q55" s="4" t="inlineStr">
@@ -5421,14 +5421,14 @@
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/zentail</t>
+          <t>https://www.ycombinator.com/companies/covera</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Covera</t>
+          <t>HemlockLos Angeles</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>https://www.covera-agents.com</t>
+          <t>https://hemlock.info</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://www.covera-agents.com/careers</t>
+          <t>https://hemlock.info/careers</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Founding GTM/ Account Executive, Work at a Startup</t>
+          <t>Software/ML/Signal Processing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coveraapp</t>
+          <t>https://www.facebook.com/hemlocklosangelesapp</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>AI-native OS for insurance brokers</t>
+          <t>Force-sensing wristband for training robotic AI</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5511,14 +5511,14 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/covera</t>
+          <t>https://www.ycombinator.com/companies/hemlock</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>HemlockLos Angeles</t>
+          <t>Lambda Robotics</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5538,17 +5538,17 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://hemlock.info</t>
+          <t>https://lambdarobotics.ai</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://hemlock.info/careers</t>
+          <t>https://lambdarobotics.ai/careers</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -5557,26 +5557,26 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Software/ML/Signal Processing Engineer, Work at a Startup</t>
+          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hemlocklosangeles</t>
+          <t>https://twitter.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHEMLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Force-sensing wristband for training robotic AI</t>
+          <t>Robotics for AI Infrastructure</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -5601,14 +5601,14 @@
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/hemlock</t>
+          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Lambda Robotics</t>
+          <t>SimanticWaterloo, ON</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -5618,60 +5618,60 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Waterloo, Canada</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai</t>
+          <t>https://simantic.dev</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai/careers</t>
+          <t>https://simantic.dev/careers</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
+          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lambdarobotics</t>
+          <t>https://www.linkedin.com/company/simanticwaterlooon</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simanticwaterloooninfo</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>Robotics for AI Infrastructure</t>
+          <t>Firmware simulation for AI agents</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5691,14 +5691,14 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
+          <t>https://www.ycombinator.com/companies/simantic</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SimanticWaterloo, ON</t>
+          <t>Locke</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5708,60 +5708,60 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Waterloo, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://simantic.dev</t>
+          <t>https://locke.inc</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://simantic.dev/careers</t>
+          <t>https://locke.inc/careers</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
+          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simanticwaterlooon</t>
+          <t>https://www.linkedin.com/company/locke</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterlooonapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/locke</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Firmware simulation for AI agents</t>
+          <t>Locke is changing the way companies and governments work together.</t>
         </is>
       </c>
       <c r="Q59" s="4" t="inlineStr">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/simantic</t>
+          <t>https://www.ycombinator.com/companies/locke</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Dawn Industries</t>
+          <t>83 Sciences</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5813,45 +5813,45 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>https://www.dawnxr.com</t>
+          <t>https://83sciences.ai</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://www.dawnxr.com/careers</t>
+          <t>https://83sciences.ai/careers</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Systems Software Engineer - Cell Modeling, Systems Software Engineer - Live Ingestion, Work at a Startup</t>
+          <t>Founding AI Engineer, Head of Sales / Founding GTM, Full-Stack Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/83sciences</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/dawnindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dawnindustriesapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dawnindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>Automatic Diagnosis &amp; Fix for Industrial Automation Cells</t>
+          <t>AI-native materials discovery powered by unpublished experimental data</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/dawn-industries</t>
+          <t>https://www.ycombinator.com/companies/83-sciences</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Locke</t>
+          <t>WaybillGurugram, HR</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5898,50 +5898,50 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://locke.inc</t>
+          <t>https://www.waybill.to</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://locke.inc/careers</t>
+          <t>https://www.waybill.to/careers</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/locke</t>
+          <t>https://x.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Locke is changing the way companies and governments work together.</t>
+          <t>Managed procurement &amp; inventory for hardware teams.</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/locke</t>
+          <t>https://www.ycombinator.com/companies/waybill</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>83 Sciences</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -5993,40 +5993,40 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://83sciences.ai</t>
+          <t>https://aktoria.com</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://83sciences.ai/careers</t>
+          <t>https://aktoria.com/careers</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Founding AI Engineer, Head of Sales / Founding GTM, Full-Stack Software Engineer, Work at a Startup</t>
+          <t>Robotics Operations Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciencesinfo</t>
+          <t>https://www.facebook.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>AI-native materials discovery powered by unpublished experimental data</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6051,14 +6051,14 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/83-sciences</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>WaybillGurugram, HR</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6068,27 +6068,27 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://www.waybill.to</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://www.waybill.to/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/bloomy</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bloomyinfo</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCWAYBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Managed procurement &amp; inventory for hardware teams.</t>
+          <t>AI-powered mastery learning for K-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/waybill</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6173,40 +6173,40 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/screenpipeapp</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSCREtrack</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>AI-powered mastery learning for K-12</t>
+          <t>AI powered by everything you've seen, said or heard</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -6277,16 +6277,16 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/coach</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/coach</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6353,17 +6353,17 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
@@ -6371,22 +6371,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coachapp</t>
+          <t>https://www.facebook.com/gutgutgooseinc</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6476,22 +6476,22 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/synapsesemiconductordurhamncinc</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
+          <t>https://www.youtube.com/channel/UCSYNAtrack</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>Personalized probiotics, guaranteed to colonize.</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -6528,45 +6528,45 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/torus</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/synapsesemiconductordurhamncapp</t>
+          <t>https://www.facebook.com/torus</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,27 +6608,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria-robotics.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -6637,41 +6637,41 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aktoriaroboticsapp</t>
+          <t>https://www.facebook.com/parasma</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPARAtrack</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6708,17 +6708,17 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6727,21 +6727,21 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/huscarl</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -6817,26 +6817,26 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>https://twitter.com/intelligencefactory</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6888,45 +6888,45 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ooakdata</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ooakdata</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTORUtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -7001,27 +7001,27 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/kugelaudio</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/kugelaudioapp</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kugelaudio</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -7073,30 +7073,30 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -7177,31 +7177,31 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudio</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7253,35 +7253,35 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/klaimee</t>
+          <t>https://twitter.com/astraea</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/asendiaai</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/asendiaai</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASENtrack</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,70 +7418,70 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/astraea</t>
+          <t>https://twitter.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraea</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinfo</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/astraea</t>
+          <t>https://www.instagram.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCREVNtrack</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7608,17 +7608,17 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -7627,21 +7627,21 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/unowallet</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREVNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7703,17 +7703,17 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7721,27 +7721,27 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/runtime</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinfo</t>
+          <t>https://www.facebook.com/runtimeinfo</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agentphone</t>
+          <t>https://x.com/characterquilt</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneapp</t>
+          <t>https://www.facebook.com/characterquiltapp</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -7897,41 +7897,41 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/runtime</t>
+          <t>https://twitter.com/manicule</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeinfo</t>
+          <t>https://www.facebook.com/maniculeinc</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7973,45 +7973,45 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/characterquilt</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/openwork</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/openworkinc</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/characterquilt</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/arzana</t>
+          <t>https://x.com/arzana</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARZAtrack</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
@@ -8128,7 +8128,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,45 +8153,45 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/openwork</t>
+          <t>https://x.com/edenrobotics</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/openworkinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,55 +8243,55 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.dev</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.dev/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Technical Writer &amp; Content Strategist, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>https://www.linkedin.com/company/aquashield</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/aquashield</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeinfo</t>
+          <t>https://www.facebook.com/aquashieldinfo</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMANItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,27 +8351,27 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/edenrobotics</t>
+          <t>https://x.com/anoria</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edenrobotics</t>
+          <t>https://www.facebook.com/anoriainfo</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/anoria</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aquashield</t>
+          <t>https://www.linkedin.com/company/ardent</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aquashield</t>
+          <t>https://x.com/ardent</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8466,12 +8466,12 @@
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARDEtrack</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/anoria</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8603,45 +8603,45 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tasklet</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tasklet</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8693,35 +8693,35 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8778,30 +8778,30 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soriaapp</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -8887,41 +8887,41 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arainfo</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASEOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,27 +8948,27 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -8981,22 +8981,22 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/soria</t>
+          <t>https://x.com/minicor</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/minicorinfo</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9053,17 +9053,17 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>https://www.linkedin.com/company/rivermarkets</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/rivermarketsinfo</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9143,45 +9143,45 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/complir</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minicorapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/complir</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9228,50 +9228,50 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsinfo</t>
+          <t>https://www.facebook.com/biostackplatforms</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9337,31 +9337,31 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/complir</t>
+          <t>https://x.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirapp</t>
+          <t>https://www.facebook.com/lumiusdurhamncapp</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>Adialante</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>http://www.adialante.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>http://www.adialante.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9427,26 +9427,26 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>https://www.linkedin.com/company/adialante</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lumiusdurhamnc</t>
+          <t>https://twitter.com/adialante</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamncinc</t>
+          <t>https://www.facebook.com/adialanteapp</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Cancer screening without barriers</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/adialante</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Gojiberry AI</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9498,45 +9498,45 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.gojiberry.ai</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.gojiberry.ai/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sales Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>https://www.linkedin.com/company/gojiberryai</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/biostackplatforms</t>
+          <t>https://x.com/gojiberryai</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gojiberryaiinc</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>AI Go-To-Market agents for B2B teams</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/gojiberry-ai</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
+    <col width="51" customWidth="1" min="13" max="13"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,55 +578,55 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/mason</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tovala</t>
+          <t>https://twitter.com/mason</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainc</t>
+          <t>https://www.facebook.com/mason</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,27 +668,27 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -697,21 +697,21 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/billiontoone</t>
+          <t>https://x.com/tovala</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,27 +758,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mason</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mason</t>
+          <t>https://twitter.com/billiontoone</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mason</t>
+          <t>https://www.facebook.com/billiontooneinc</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/billiontoone</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -877,21 +877,21 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/isonohealth</t>
+          <t>https://twitter.com/soundboks</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>https://www.linkedin.com/company/isonohealth</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboksapp</t>
+          <t>https://www.facebook.com/isonohealthinfo</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/isonohealth</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgramapp</t>
+          <t>https://www.facebook.com/deepgram</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDEEPtrack</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/mux</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/humaninterest</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/mux</t>
+          <t>https://twitter.com/humaninterest</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/instaworkinc</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/instawork</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lattice</t>
+          <t>https://www.facebook.com/latticeinc</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1468,7 +1468,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Xendit</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1478,60 +1478,60 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://www.xendit.co</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://www.xendit.co/careers</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Senior Software Engineer - Platform, Work at a Startup</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/eightsleep</t>
+          <t>https://x.com/xendit</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eightsleep</t>
+          <t>https://www.instagram.com/xendit</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>Provides payment infrastructure for Southeast Asia</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/xendit</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Xendit</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1568,55 +1568,55 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>https://www.xendit.co</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.xendit.co/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/xendit</t>
+          <t>https://x.com/eightsleep</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/eightsleepinc</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Provides payment infrastructure for Southeast Asia</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/xendit</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Shape (ShapeScale)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>https://shapescale.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>https://shapescale.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Senior iOS Developer, Work at a Startup</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/shapeshapescale</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Shape (ShapeScale)</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Senior iOS Developer, Work at a Startup</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/shapeshapescale</t>
+          <t>https://twitter.com/bitmovin</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>Drip CapitalMH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2028,22 +2028,22 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>http://dripcapital.com</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>http://dripcapital.com/careers</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2056,17 +2056,17 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomicsapp</t>
+          <t>https://www.facebook.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Digital trade finance and B2B commerce company</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/drip-capital</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Drip CapitalMH</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>http://dripcapital.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>http://dripcapital.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/vergegenomics</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Digital trade finance and B2B commerce company</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/drip-capital</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/reachinc</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/reach</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2416,22 +2416,22 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/branch8app</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/branch8</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/snapmagic</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/snapmagic</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gemnote</t>
+          <t>New Story</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>http://gemnote.com</t>
+          <t>http://newstoryhomes.org</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>http://gemnote.com/careers</t>
+          <t>http://newstoryhomes.org/careers</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Head of Operations, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gemnote</t>
+          <t>https://www.linkedin.com/company/newstory</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/gemnote</t>
+          <t>https://twitter.com/newstory</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/newstory</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Gemnote is the easiest way to design, create and send custom products.</t>
+          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gemnote</t>
+          <t>https://www.ycombinator.com/companies/new-story</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>New Story</t>
+          <t>Gemnote</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2648,50 +2648,50 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org</t>
+          <t>http://gemnote.com</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org/careers</t>
+          <t>http://gemnote.com/careers</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Head of Operations, Work at a Startup</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/gemnote</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/gemnote</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
+          <t>Gemnote is the easiest way to design, create and send custom products.</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/new-story</t>
+          <t>https://www.ycombinator.com/companies/gemnote</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/luggsaltlakecityut</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityut</t>
+          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mashgininc</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/quartzy</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzy</t>
+          <t>https://www.facebook.com/quartzyinfo</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/quartzy</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/taraai</t>
+          <t>https://x.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taraaiinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/tab</t>
+          <t>https://x.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabapp</t>
+          <t>https://www.facebook.com/tabinc</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streakapp</t>
+          <t>https://www.facebook.com/streakinc</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/giveffect</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/giveffectapp</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3501,22 +3501,22 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/onesignalapp</t>
+          <t>https://www.facebook.com/onesignal</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCONEStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/qventus</t>
+          <t>https://twitter.com/qventus</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventusapp</t>
+          <t>https://www.facebook.com/qventusinc</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHACKtrack</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/apollo</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/apolloinc</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hive</t>
+          <t>https://twitter.com/hive</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveapp</t>
+          <t>https://www.facebook.com/hiveinfo</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/picnicai</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/picnicai</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPICNtrack</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/piinpoint</t>
+          <t>https://twitter.com/piinpoint</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpointinc</t>
+          <t>https://www.facebook.com/piinpoint</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPIINtrack</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempoinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTEMPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/noorahealthtraversecity</t>
+          <t>https://twitter.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCNOORtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Cambly</t>
+          <t>AptDeco</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -4358,27 +4358,27 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>http://www.cambly.com</t>
+          <t>https://www.aptdeco.com</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>http://www.cambly.com/careers</t>
+          <t>https://www.aptdeco.com/careers</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -4387,11 +4387,11 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -4401,17 +4401,17 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/cambly</t>
+          <t>https://x.com/aptdeco</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/camblyinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cambly</t>
+          <t>https://www.instagram.com/aptdeco</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>On-demand access to English tutors over video chat.</t>
+          <t>AptDeco is the easiest way to buy and sell used furniture</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/cambly</t>
+          <t>https://www.ycombinator.com/companies/aptdeco</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>AptDeco</t>
+          <t>Cambly</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4458,40 +4458,40 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com</t>
+          <t>http://www.cambly.com</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com/careers</t>
+          <t>http://www.cambly.com/careers</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>https://www.linkedin.com/company/cambly</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aptdeco</t>
+          <t>https://x.com/cambly</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>AptDeco is the easiest way to buy and sell used furniture</t>
+          <t>On-demand access to English tutors over video chat.</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aptdeco</t>
+          <t>https://www.ycombinator.com/companies/cambly</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4576,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lob</t>
+          <t>https://x.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lob</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbellyinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGOLDtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/simplyinsured</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/simplyinsured</t>
+          <t>https://x.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsuredinc</t>
+          <t>https://www.facebook.com/simplyinsuredapp</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circuithubinfo</t>
+          <t>https://www.facebook.com/circuithubinc</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circuithub</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/radar</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/influxdata</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINFLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/etleap</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleapinc</t>
+          <t>https://www.facebook.com/etleapinfo</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCETLEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5301,17 +5301,17 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/zentail</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coveraapp</t>
+          <t>https://www.facebook.com/coverainc</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5481,17 +5481,17 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangelesapp</t>
+          <t>https://www.facebook.com/hemlocklosangelesinfo</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lambdarobotics</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterloooninfo</t>
+          <t>https://www.facebook.com/simanticwaterlooonapp</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/locke</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lockeinc</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Locke is changing the way companies and governments work together.</t>
+          <t>AI agents that help companies and governments work together.</t>
         </is>
       </c>
       <c r="Q59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/83sciences</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UC83SCtrack</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -5968,7 +5968,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://rational.to</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://rational.to/careers</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -6007,26 +6007,26 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>Forward-Deployed Engineer, Machine Learning Researcher, Software Engineering Intern, Applied AI</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>https://www.linkedin.com/company/rational</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aktoriarobotics</t>
+          <t>https://twitter.com/rational</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRATItrack</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI Employees for Accounting</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/rational</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomyinfo</t>
+          <t>https://www.facebook.com/bloomyinc</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipeapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/screenpipe</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>AI powered by everything you've seen, said or heard</t>
+          <t>Turn your company's computer work into AI agents.</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6291,17 +6291,17 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/coach</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coachapp</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
@@ -6381,17 +6381,17 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/gutgutgoose</t>
+          <t>https://twitter.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgooseinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gutgutgoose</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/synapsesemiconductordurhamncinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSYNAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -6528,45 +6528,45 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://aktoria-robotics.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6618,45 +6618,45 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ooakdata</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/parasma</t>
+          <t>https://www.facebook.com/ooakdataapp</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPARAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6727,31 +6727,31 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/torus</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/torus</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -6817,41 +6817,41 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Data Engineer (India), Work at a Startup</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/intelligencefactory</t>
+          <t>https://twitter.com/parasma</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/parasma</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/parasma</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,55 +6878,55 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,70 +6968,70 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioapp</t>
+          <t>https://www.facebook.com/intelligencefactoryapp</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>KugelAudio</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -7073,40 +7073,40 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/kugelaudio</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/kugelaudio</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/kugelaudioapp</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKUGEtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/klaimee</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKLAItrack</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7253,35 +7253,35 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/astraea</t>
+          <t>https://x.com/arloindustries</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARLOtrack</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7343,55 +7343,55 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/asendiaai</t>
+          <t>https://twitter.com/astraea</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -7428,17 +7428,17 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -7451,37 +7451,37 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREVNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,45 +7508,45 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -7636,17 +7636,17 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/unowallet</t>
+          <t>https://twitter.com/unowallet</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/unowalletinc</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7678,7 +7678,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -7731,27 +7731,27 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/runtime</t>
+          <t>https://twitter.com/agentphone</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeinfo</t>
+          <t>https://www.facebook.com/agentphoneinc</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAGENtrack</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/characterquilt</t>
+          <t>https://www.linkedin.com/company/runtime</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquiltapp</t>
+          <t>https://www.facebook.com/runtimeinc</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/runtime</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,17 +7883,17 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
@@ -7901,22 +7901,22 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/manicule</t>
+          <t>https://twitter.com/characterquilt</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeinc</t>
+          <t>https://www.facebook.com/characterquiltinc</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7968,50 +7968,50 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/openwork</t>
+          <t>https://x.com/arzana</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/openworkinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8058,40 +8058,40 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arzana</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/arzana</t>
+          <t>https://twitter.com/openwork</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARZAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -8167,31 +8167,31 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/maniculeinfo</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -8261,27 +8261,27 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aquashield</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aquashield</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aquashieldinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,27 +8351,27 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>https://www.linkedin.com/company/aquashield</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/anoria</t>
+          <t>https://x.com/aquashield</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoriainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/ardent</t>
+          <t>https://x.com/anoria</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8461,17 +8461,17 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/anoria</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARDEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -8531,27 +8531,27 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>https://www.linkedin.com/company/ardent</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>https://twitter.com/ardent</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ardentinc</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ardent</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8603,40 +8603,40 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tasklet</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tasklet</t>
+          <t>https://www.facebook.com/kuliinfo</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8693,40 +8693,40 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/taskletinfo</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,55 +8768,55 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soriaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,32 +8858,32 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -8901,27 +8901,27 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/soria</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arainfo</t>
+          <t>https://www.facebook.com/soriainfo</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>https://www.instagram.com/soria</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSORItrack</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8963,17 +8963,17 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
@@ -8981,27 +8981,27 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minicorinfo</t>
+          <t>https://www.facebook.com/araapp</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -9053,17 +9053,17 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rivermarkets</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
@@ -9086,22 +9086,22 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/minicor</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9143,45 +9143,45 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>https://www.linkedin.com/company/rivermarkets</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/complir</t>
+          <t>https://x.com/rivermarkets</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/rivermarketsinc</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/complir</t>
+          <t>https://www.instagram.com/rivermarkets</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,60 +9218,60 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatforms</t>
+          <t>https://www.facebook.com/complirapp</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9346,27 +9346,27 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/lumiusdurhamnc</t>
+          <t>https://twitter.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamncapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLUMItrack</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
@@ -9388,7 +9388,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Adialante</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,60 +9398,60 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/adialante</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/adialante</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/adialanteapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Cancer screening without barriers</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/adialante</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Gojiberry AI</t>
+          <t>Adialante</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.gojiberry.ai</t>
+          <t>http://www.adialante.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.gojiberry.ai/careers</t>
+          <t>http://www.adialante.com/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -9517,26 +9517,26 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Sales Development Representative, Work at a Startup</t>
+          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gojiberryai</t>
+          <t>https://www.linkedin.com/company/adialante</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/gojiberryai</t>
+          <t>https://x.com/adialante</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gojiberryaiinc</t>
+          <t>https://www.facebook.com/adialanteinfo</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCADIAtrack</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>AI Go-To-Market agents for B2B teams</t>
+          <t>Cancer screening without barriers</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gojiberry-ai</t>
+          <t>https://www.ycombinator.com/companies/adialante</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,8 +464,8 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="47" customWidth="1" min="12" max="12"/>
-    <col width="51" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
     <col width="53" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -588,50 +588,50 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mason</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/mason</t>
+          <t>https://twitter.com/tovala</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mason</t>
+          <t>https://www.facebook.com/tovala</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,60 +668,60 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/mason</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/masoninfo</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mason</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -801,22 +801,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/billiontoone</t>
+          <t>https://x.com/billiontoone</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontooneinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBILLtrack</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -858,45 +858,45 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/isonohealth</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/isonohealth</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -948,35 +948,35 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/isonohealth</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealthinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/isonohealth</t>
+          <t>https://www.instagram.com/soundboks</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/deepgram</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/muxinc</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instaworkinc</t>
+          <t>https://www.facebook.com/instaworkapp</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINSTtrack</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/latticeinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLATTtrack</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/xendit</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Shape (ShapeScale)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1578,50 +1578,50 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://shapescale.com</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://shapescale.com/careers</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Senior iOS Developer, Work at a Startup</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>https://www.linkedin.com/company/shapeshapescale</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinc</t>
+          <t>https://www.facebook.com/shapeshapescaleinc</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Shape (ShapeScale)</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1668,45 +1668,45 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://shapescale.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Senior iOS Developer, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/shapeshapescale</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/eightsleep</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/eightsleepinc</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/circlemedical</t>
+          <t>https://twitter.com/circlemedical</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circlemedical</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bitmovin</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1966,17 +1966,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/givecampus</t>
+          <t>https://twitter.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/givecampusapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Drip CapitalMH</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2018,27 +2018,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>http://dripcapital.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>http://dripcapital.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2056,22 +2056,22 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/vergegenomics</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dripcapitalmh</t>
+          <t>https://www.facebook.com/vergegenomicsinc</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/vergegenomics</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Digital trade finance and B2B commerce company</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/drip-capital</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>Drip CapitalMH</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>http://dripcapital.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>http://dripcapital.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/dripcapitalmh</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Digital trade finance and B2B commerce company</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/drip-capital</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agilemd</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2326,22 +2326,22 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/reach</t>
+          <t>https://x.com/reach</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachinc</t>
+          <t>https://www.facebook.com/reachinfo</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/branch8</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8app</t>
+          <t>https://www.facebook.com/branch8info</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/snapmagicinfo</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>New Story</t>
+          <t>Gemnote</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2558,60 +2558,60 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org</t>
+          <t>http://gemnote.com</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>http://newstoryhomes.org/careers</t>
+          <t>http://gemnote.com/careers</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Head of Operations, Work at a Startup</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newstory</t>
+          <t>https://www.linkedin.com/company/gemnote</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gemnote</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
+          <t>Gemnote is the easiest way to design, create and send custom products.</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/new-story</t>
+          <t>https://www.ycombinator.com/companies/gemnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Gemnote</t>
+          <t>New Story</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>http://gemnote.com</t>
+          <t>http://newstoryhomes.org</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>http://gemnote.com/careers</t>
+          <t>http://newstoryhomes.org/careers</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Head of Operations, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gemnote</t>
+          <t>https://www.linkedin.com/company/newstory</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/newstory</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Gemnote is the easiest way to design, create and send custom products.</t>
+          <t>We pioneer solutions to end the global housing crisis by empowering…</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gemnote</t>
+          <t>https://www.ycombinator.com/companies/new-story</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironcladapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mashgin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashgininc</t>
+          <t>https://www.facebook.com/mashginapp</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mashgin</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/quartzy</t>
+          <t>https://x.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzyinfo</t>
+          <t>https://www.facebook.com/quartzyinc</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tab</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabinc</t>
+          <t>https://www.facebook.com/tab</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tab</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streakinc</t>
+          <t>https://www.facebook.com/streak</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/giveffect</t>
+          <t>https://twitter.com/giveffect</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>https://twitter.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/magicapp</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventusinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hackerrank</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/hackerrank</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hackerrankapp</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHACKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloinc</t>
+          <t>https://www.facebook.com/apolloapp</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3956,17 +3956,17 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hive</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHIVEtrack</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/picnicai</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPICNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/piinpoint</t>
+          <t>https://x.com/piinpoint</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpoint</t>
+          <t>https://www.facebook.com/piinpointinfo</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPIINtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tempo</t>
+          <t>https://x.com/tempo</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tempo</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCNOORtrack</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>AptDeco</t>
+          <t>Cambly</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -4358,60 +4358,60 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com</t>
+          <t>http://www.cambly.com</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.aptdeco.com/careers</t>
+          <t>http://www.cambly.com/careers</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/cambly</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/camblyinfo</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>AptDeco is the easiest way to buy and sell used furniture</t>
+          <t>On-demand access to English tutors over video chat.</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aptdeco</t>
+          <t>https://www.ycombinator.com/companies/cambly</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Cambly</t>
+          <t>AptDeco</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4448,50 +4448,50 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>http://www.cambly.com</t>
+          <t>https://www.aptdeco.com</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>http://www.cambly.com/careers</t>
+          <t>https://www.aptdeco.com/careers</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Partnership Manager - Transportation &amp; Logistics, Customer Care Associate, Marketing Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/cambly</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAPTDtrack</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>On-demand access to English tutors over video chat.</t>
+          <t>AptDeco is the easiest way to buy and sell used furniture</t>
         </is>
       </c>
       <c r="Q45" s="4" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/cambly</t>
+          <t>https://www.ycombinator.com/companies/aptdeco</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lobinc</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/goldbellyapp</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/goldbelly</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simplyinsured</t>
+          <t>https://twitter.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsuredapp</t>
+          <t>https://www.facebook.com/simplyinsured</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simplyinsured</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4851,22 +4851,22 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circuithubinc</t>
+          <t>https://www.facebook.com/circuithub</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4941,22 +4941,22 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/radarinc</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRADAtrack</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/influxdata</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/influxdatainfo</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/etleap</t>
+          <t>https://x.com/etleap</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleapinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCETLEtrack</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/padlet</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/padlet</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/padletinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/zentailinfo</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCZENTtrack</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/covera</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/covera</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/covera</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5476,22 +5476,22 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/hemlocklosangeles</t>
+          <t>https://x.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangelesinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lambdarobotics</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLAMBtrack</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/simanticwaterlooon</t>
+          <t>https://x.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5746,17 +5746,17 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/locke</t>
+          <t>https://x.com/locke</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lockeinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5846,17 +5846,17 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/83sciencesinfo</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC83SCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5926,22 +5926,22 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/rationalinfo</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/rational</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRATItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomyinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bloomy</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6196,17 +6196,17 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/screenpipe</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/screenpipeinfo</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
@@ -6291,17 +6291,17 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/coach</t>
+          <t>https://x.com/coach</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coachapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/coach</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -6598,7 +6598,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6618,50 +6618,50 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/ooakdata</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdataapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/parasma</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6708,50 +6708,50 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ooakdata</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torus</t>
+          <t>https://www.facebook.com/ooakdatainfo</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6803,45 +6803,45 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/huscarlinfo</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/huscarl</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryapp</t>
+          <t>https://www.facebook.com/intelligencefactory</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudio</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKUGEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/klaimee</t>
+          <t>https://x.com/klaimee</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/klaimee</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKLAItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
@@ -7291,12 +7291,12 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/arloindustries</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARLOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/astraea</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/astraeaapp</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -7466,17 +7466,17 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/asendiaaiinc</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/asendiaai</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASENtrack</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
@@ -7641,17 +7641,17 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/unowallet</t>
+          <t>https://x.com/unowallet</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinc</t>
+          <t>https://www.facebook.com/unowalletinfo</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/unowallet</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7726,22 +7726,22 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/agentphone</t>
+          <t>https://x.com/agentphone</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneinc</t>
+          <t>https://www.facebook.com/agentphoneapp</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -7816,27 +7816,27 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/runtime</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeinc</t>
+          <t>https://www.facebook.com/runtimeinfo</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquiltinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/characterquilt</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCHARtrack</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7996,27 +7996,27 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arzanainc</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/arzana</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARZAtrack</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -8038,7 +8038,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -8077,26 +8077,26 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/openwork</t>
+          <t>https://twitter.com/manicule</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/maniculeapp</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMANItrack</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,30 +8153,30 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeinfo</t>
+          <t>https://www.facebook.com/openwork</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCOPENtrack</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,17 +8243,17 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
@@ -8261,17 +8261,17 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>https://twitter.com/aquashield</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>https://www.instagram.com/aquashield</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aquashield</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aquashield</t>
+          <t>https://x.com/edenrobotics</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/edenroboticsinfo</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8536,22 +8536,22 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kuliinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kuli</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
@@ -8716,22 +8716,22 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tasklet</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taskletinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aseonlabsapp</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/aseonlabs</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASEOtrack</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
@@ -8896,17 +8896,17 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soria</t>
+          <t>https://x.com/soria</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soriainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSORItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/araapp</t>
+          <t>https://www.facebook.com/arainfo</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9076,12 +9076,12 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/minicor</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9166,27 +9166,27 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsinc</t>
+          <t>https://www.facebook.com/rivermarketsinfo</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
@@ -9298,7 +9298,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,50 +9308,50 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLUMItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9408,35 +9408,35 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>https://www.instagram.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/adialanteinfo</t>
+          <t>https://www.facebook.com/adialante</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCADIAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -453,7 +453,7 @@
   <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -465,7 +465,7 @@
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
     <col width="53" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,60 +578,60 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovala</t>
+          <t>https://www.facebook.com/billiontooneinc</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/masoninfo</t>
+          <t>https://www.facebook.com/mason</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,55 +758,55 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tovalainc</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBILLtrack</t>
+          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -896,12 +896,12 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/isonohealth</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,50 +938,50 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/deepgram</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soundboks</t>
+          <t>https://www.instagram.com/deepgram</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1038,30 +1038,30 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/soundboks</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDEEPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Lattice</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1133,40 +1133,40 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>https://lattice.com</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>https://lattice.com/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>https://www.linkedin.com/company/lattice</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/mux</t>
+          <t>https://twitter.com/lattice</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxinc</t>
+          <t>https://www.facebook.com/latticeinfo</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>Modern people management platform.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/lattice</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/humaninterest</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Instawork</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1313,55 +1313,55 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>http://instawork.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>http://instawork.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/instawork</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instaworkapp</t>
+          <t>https://www.facebook.com/muxapp</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instawork</t>
+          <t>https://www.instagram.com/mux</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINSTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>A flexible work app that connects businesses with hourly workers.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/instawork</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Lattice</t>
+          <t>Instawork</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1403,35 +1403,35 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>https://lattice.com</t>
+          <t>http://instawork.com</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://lattice.com/careers</t>
+          <t>http://instawork.com/careers</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/instawork</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLATTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>Modern people management platform.</t>
+          <t>A flexible work app that connects businesses with hourly workers.</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lattice</t>
+          <t>https://www.ycombinator.com/companies/instawork</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/xendit</t>
+          <t>https://twitter.com/xendit</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1606,22 +1606,22 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shapeshapescaleinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1648,7 +1648,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,32 +1658,32 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1691,22 +1691,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinc</t>
+          <t>https://www.facebook.com/circlemedicalapp</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>GiveCampus</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1758,40 +1758,40 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>http://go.givecampus.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>http://go.givecampus.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
+          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/circlemedical</t>
+          <t>https://x.com/givecampus</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>The fundraising platform for schools.</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/givecampus</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/eightsleep</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/eightsleep</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GiveCampus</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>https://www.linkedin.com/company/bitmovin</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/givecampus</t>
+          <t>https://twitter.com/bitmovin</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bitmovinapp</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>The fundraising platform for schools.</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/givecampus</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Verge Genomics</t>
+          <t>Drip CapitalMH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2018,27 +2018,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com</t>
+          <t>http://dripcapital.com</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>http://vergegenomics.com/careers</t>
+          <t>http://dripcapital.com/careers</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vergegenomics</t>
+          <t>https://www.linkedin.com/company/dripcapitalmh</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2066,22 +2066,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomicsinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vergegenomics</t>
+          <t>https://www.instagram.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>We use human data and AI to develop better drugs faster.</t>
+          <t>Digital trade finance and B2B commerce company</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/verge-genomics</t>
+          <t>https://www.ycombinator.com/companies/drip-capital</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Drip CapitalMH</t>
+          <t>Verge Genomics</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2108,27 +2108,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>http://dripcapital.com</t>
+          <t>http://vergegenomics.com</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>http://dripcapital.com/careers</t>
+          <t>http://vergegenomics.com/careers</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dripcapitalmh</t>
+          <t>https://www.linkedin.com/company/vergegenomics</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/vergegenomicsapp</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Digital trade finance and B2B commerce company</t>
+          <t>We use human data and AI to develop better drugs faster.</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/drip-capital</t>
+          <t>https://www.ycombinator.com/companies/verge-genomics</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agilemdapp</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/agilemd</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/reach</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8info</t>
+          <t>https://www.facebook.com/branch8app</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/snapmagicinfo</t>
+          <t>https://www.facebook.com/snapmagicapp</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/gemnote</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gemnote</t>
+          <t>https://www.facebook.com/gemnoteapp</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/newstoryapp</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ironclad</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ironclad</t>
+          <t>https://twitter.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCIRONtrack</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mashgin</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashginapp</t>
+          <t>https://www.facebook.com/mashgininfo</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/quartzy</t>
+          <t>https://twitter.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzyinc</t>
+          <t>https://www.facebook.com/quartzy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/quartzy</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/taraai</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tab</t>
+          <t>https://www.facebook.com/tabinfo</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/streak</t>
+          <t>https://x.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/streak</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffectapp</t>
+          <t>https://www.facebook.com/giveffectinfo</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/giveffect</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/onesignal</t>
+          <t>https://www.facebook.com/onesignalinfo</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/onesignal</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCONEStrack</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3586,17 +3586,17 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/magic</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/magic</t>
+          <t>https://x.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/magicapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/qventus</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/qventus</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrankapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hive</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3956,17 +3956,17 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hiveinfo</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/picnicaiinfo</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/picnicai</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpointinfo</t>
+          <t>https://www.facebook.com/piinpointinc</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/piinpoint</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4168,7 +4168,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Noora HealthTraverse City</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Traverse City, MI</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>http://noorahealth.org</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>http://noorahealth.org/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -4211,27 +4211,27 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tempo</t>
+          <t>https://x.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempo</t>
+          <t>https://www.facebook.com/noorahealthtraversecityinc</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>Training patients and their families with health skills</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/noora-health</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Noora HealthTraverse City</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Traverse City, MI</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>http://noorahealth.org</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>http://noorahealth.org/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4301,37 +4301,37 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tempo</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/noorahealthtraversecity</t>
+          <t>https://www.facebook.com/tempoinfo</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCNOORtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Training patients and their families with health skills</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/noora-health</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPTDtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4576,22 +4576,22 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lob</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lobinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/goldbelly</t>
+          <t>https://twitter.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbellyapp</t>
+          <t>https://www.facebook.com/goldbelly</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsured</t>
+          <t>https://www.facebook.com/simplyinsuredinfo</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSIMPtrack</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4851,22 +4851,22 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circuithub</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4936,27 +4936,27 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/radar</t>
+          <t>https://x.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radarinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/radar</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRADAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,17 +5026,17 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/influxdata</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/influxdata</t>
+          <t>https://x.com/influxdata</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/influxdatainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINFLtrack</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/etleapapp</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCETLEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/padlet</t>
+          <t>https://x.com/padlet</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5391,22 +5391,22 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/covera</t>
+          <t>https://twitter.com/covera</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coverainc</t>
+          <t>https://www.facebook.com/coveraapp</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/hemlocklosangeles</t>
+          <t>https://twitter.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hemlocklosangelesinc</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lambdarobotics</t>
+          <t>https://x.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLAMBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/locke</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciencesinfo</t>
+          <t>https://www.facebook.com/83sciences</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/83sciences</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhr</t>
+          <t>https://www.facebook.com/waybillgurugramhrinc</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rational</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>AI Employees for Accounting</t>
+          <t>AI Employees for In-House Enterprise Accounting</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6058,7 +6058,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://aktoria.com</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://aktoria.com/careers</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Robotics Operations Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aktoriaroboticsinfo</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bloomy</t>
+          <t>https://www.instagram.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>AI-powered mastery learning for K-12</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -6173,55 +6173,55 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/screenpipe</t>
+          <t>https://twitter.com/bloomy</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipeinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/screenpipe</t>
+          <t>https://www.instagram.com/bloomy</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSCREtrack</t>
+          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>Turn your company's computer work into AI agents.</t>
+          <t>AI-driven 1-to-1 learning for every student</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6263,55 +6263,55 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coach</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ooakdata</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCOOAKtrack</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6353,35 +6353,35 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/gutgutgoose</t>
+          <t>https://x.com/screenpipe</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>Turn your company's computer work into AI agents.</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,27 +6428,27 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -6471,17 +6471,17 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/synapsesemiconductordurhamnc</t>
+          <t>https://twitter.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gutgutgooseinfo</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gutgutgoose</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -6528,35 +6528,35 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria-robotics.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>https://www.linkedin.com/company/coach</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,27 +6608,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -6641,27 +6641,27 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>https://twitter.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,55 +6698,55 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdatainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/torusapp</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarlinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/intelligencefactory</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactory</t>
+          <t>https://www.facebook.com/intelligencefactoryinfo</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -7048,7 +7048,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KugelAudio</t>
+          <t>KugelAudioBerlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudio</t>
+          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioapp</t>
+          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinfo</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKUGEtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
@@ -7191,17 +7191,17 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/klaimee</t>
+          <t>https://twitter.com/klaimee</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/klaimee</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/astraea</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeaapp</t>
+          <t>https://www.facebook.com/astraeainc</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
@@ -7456,27 +7456,27 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/asendiaai</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaaiinc</t>
+          <t>https://www.facebook.com/asendiaaiinfo</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinfo</t>
+          <t>https://www.facebook.com/unowalletapp</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/agentphone</t>
+          <t>https://twitter.com/agentphone</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneapp</t>
+          <t>https://www.facebook.com/agentphoneinc</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeinfo</t>
+          <t>https://www.facebook.com/runtime</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRUNTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/arzana</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzanainc</t>
+          <t>https://www.facebook.com/arzana</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARZAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -8038,7 +8038,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -8077,11 +8077,11 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMANItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -8167,26 +8167,26 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/manicule</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCOPENtrack</t>
+          <t>https://www.youtube.com/channel/UCMANItrack</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aquashield</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edenroboticsinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8446,17 +8446,17 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/anoria</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ardentapp</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tasklet</t>
+          <t>https://twitter.com/tasklet</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aseonlabsapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
@@ -8901,17 +8901,17 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soriaapp</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ara</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARAtrack</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9076,17 +9076,17 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/minicorinfo</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/rivermarkets</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsinfo</t>
+          <t>https://www.facebook.com/rivermarkets</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/rivermarkets</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirapp</t>
+          <t>https://www.facebook.com/complirinfo</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/complir</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9298,7 +9298,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9337,26 +9337,26 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamncinc</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>Adialante</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>http://www.adialante.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>http://www.adialante.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9427,16 +9427,16 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamnc</t>
+          <t>https://www.facebook.com/adialante</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumiusdurhamnc</t>
+          <t>https://www.instagram.com/adialante</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Cancer screening without barriers</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/adialante</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Adialante</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,70 +9488,70 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>http://www.adialante.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>http://www.adialante.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/adialante</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/adialante</t>
+          <t>https://x.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/adialante</t>
+          <t>https://www.facebook.com/biostackplatformsapp</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBIOStrack</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Cancer screening without barriers</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/adialante</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -578,12 +578,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontooneinc</t>
+          <t>https://www.facebook.com/billiontoone</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/billiontoone</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,27 +668,27 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mason</t>
+          <t>https://www.facebook.com/tovalaapp</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -863,45 +863,45 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/deepgram</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/deepgraminc</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,50 +938,50 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1038,30 +1038,30 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/latticeinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1223,55 +1223,55 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/humaninterest</t>
+          <t>https://twitter.com/mux</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/muxinc</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
+          <t>https://www.youtube.com/channel/UCMUXtrack</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1313,45 +1313,45 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>https://www.linkedin.com/company/humaninterest</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/humaninterest</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/instawork</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1606,27 +1606,27 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/shapeshapescale</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/shapeshapescale</t>
+          <t>https://x.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/shapeshapescaleinc</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSHAPtrack</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circlemedicalapp</t>
+          <t>https://www.facebook.com/circlemedicalinfo</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circlemedical</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>GiveCampus</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1758,45 +1758,45 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/givecampus</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/givecampus</t>
+          <t>https://x.com/eightsleep</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/eightsleepinc</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCEIGHtrack</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>The fundraising platform for schools.</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/givecampus</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>GiveCampus</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1848,30 +1848,30 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>http://go.givecampus.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>http://go.givecampus.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>The fundraising platform for schools.</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/givecampus</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bitmovinapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomicsapp</t>
+          <t>https://www.facebook.com/vergegenomics</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2241,22 +2241,22 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agilemdapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAGILtrack</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/reachinc</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCREACtrack</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/branch8</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/branch8</t>
+          <t>https://x.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8app</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/snapmagic</t>
+          <t>https://twitter.com/snapmagic</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/snapmagicapp</t>
+          <t>https://www.facebook.com/snapmagic</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gemnoteapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gemnote</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/newstory</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/newstoryapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/newstory</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCNEWStrack</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -2776,27 +2776,27 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ironclad</t>
+          <t>https://x.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ironcladinfo</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ironclad</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCIRONtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/luggsaltlakecityut</t>
+          <t>https://twitter.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/luggsaltlakecityutapp</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/quartzy</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/quartzy</t>
+          <t>https://x.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/taraai</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3226,17 +3226,17 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tab</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabinfo</t>
+          <t>https://www.facebook.com/tabapp</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/streak</t>
+          <t>https://twitter.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffectinfo</t>
+          <t>https://www.facebook.com/giveffect</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/onesignal</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/onesignal</t>
+          <t>https://x.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/onesignalinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCONEStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3586,17 +3586,17 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>https://twitter.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/magicinc</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/qventus</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/qventusinfo</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCQVENtrack</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hackerrankinfo</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/apollo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/apollo</t>
+          <t>https://x.com/apollo</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloapp</t>
+          <t>https://www.facebook.com/apolloinfo</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hive</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicaiinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/piinpoint</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/piinpoint</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/piinpointinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4168,7 +4168,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Noora HealthTraverse City</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Traverse City, MI</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>http://noorahealth.org</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>http://noorahealth.org/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -4211,27 +4211,27 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/noorahealthtraversecityinc</t>
+          <t>https://www.facebook.com/tempo</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Training patients and their families with health skills</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/noora-health</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Noora HealthTraverse City</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4268,27 +4268,27 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Traverse City, MI</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>http://noorahealth.org</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>http://noorahealth.org/careers</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tempo</t>
+          <t>https://twitter.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempoinfo</t>
+          <t>https://www.facebook.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCNOORtrack</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>Training patients and their families with health skills</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/noora-health</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/cambly</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/camblyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aptdecoinc</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/aptdeco</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/goldbelly</t>
+          <t>https://x.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsuredinfo</t>
+          <t>https://www.facebook.com/simplyinsured</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simplyinsured</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/radarapp</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/influxdata</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINFLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5121,17 +5121,17 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/etleap</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleapapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/etleap</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/padlet</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/zentail</t>
+          <t>https://x.com/zentail</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCZENTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Covera</t>
+          <t>The Subvocal Company</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5363,55 +5363,55 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://www.covera-agents.com</t>
+          <t>https://subvocal.company</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.covera-agents.com/careers</t>
+          <t>https://subvocal.company/careers</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Founding GTM/ Account Executive, Work at a Startup</t>
+          <t>Founding Machine Learning Engineer, Founding Sensing Research Engineer, Founding Wearable Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/covera</t>
+          <t>https://www.linkedin.com/company/thesubvocalcompany</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/covera</t>
+          <t>https://x.com/thesubvocalcompany</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coveraapp</t>
+          <t>https://www.facebook.com/thesubvocalcompanyapp</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/thesubvocalcompany</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>AI-native OS for insurance brokers</t>
+          <t>Talk to your computer without talking</t>
         </is>
       </c>
       <c r="Q55" s="4" t="inlineStr">
@@ -5421,14 +5421,14 @@
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/covera</t>
+          <t>https://www.ycombinator.com/companies/the-subvocal-company</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>HemlockLos Angeles</t>
+          <t>Covera</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>https://hemlock.info</t>
+          <t>https://www.covera-agents.com</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://hemlock.info/careers</t>
+          <t>https://www.covera-agents.com/careers</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5471,27 +5471,27 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Software/ML/Signal Processing Engineer, Work at a Startup</t>
+          <t>Founding GTM/ Account Executive, Work at a Startup</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
+          <t>https://www.linkedin.com/company/covera</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/hemlocklosangeles</t>
+          <t>https://x.com/covera</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangelesinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/covera</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>Force-sensing wristband for training robotic AI</t>
+          <t>AI-native OS for insurance brokers</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -5511,14 +5511,14 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/hemlock</t>
+          <t>https://www.ycombinator.com/companies/covera</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Lambda Robotics</t>
+          <t>HemlockLos Angeles</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5538,45 +5538,45 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai</t>
+          <t>https://hemlock.info</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai/careers</t>
+          <t>https://hemlock.info/careers</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
+          <t>Software/ML/Signal Processing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lambdarobotics</t>
+          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hemlocklosangelesinc</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Robotics for AI Infrastructure</t>
+          <t>Force-sensing wristband for training robotic AI</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -5601,14 +5601,14 @@
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
+          <t>https://www.ycombinator.com/companies/hemlock</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>SimanticWaterloo, ON</t>
+          <t>Lambda Robotics</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -5628,17 +5628,17 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Waterloo, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://simantic.dev</t>
+          <t>https://lambdarobotics.ai</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://simantic.dev/careers</t>
+          <t>https://lambdarobotics.ai/careers</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -5647,41 +5647,41 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
+          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterlooonapp</t>
+          <t>https://www.facebook.com/lambdarobotics</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lambdarobotics</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSIMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>Firmware simulation for AI agents</t>
+          <t>Robotics for AI Infrastructure</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5691,14 +5691,14 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/simantic</t>
+          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Locke</t>
+          <t>SimanticWaterloo, ON</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5718,17 +5718,17 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Waterloo, Canada</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://locke.inc</t>
+          <t>https://simantic.dev</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://locke.inc/careers</t>
+          <t>https://simantic.dev/careers</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -5737,26 +5737,26 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
+          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/locke</t>
+          <t>https://twitter.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simanticwaterlooonapp</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>AI agents that help companies and governments work together.</t>
+          <t>Firmware simulation for AI agents</t>
         </is>
       </c>
       <c r="Q59" s="4" t="inlineStr">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/locke</t>
+          <t>https://www.ycombinator.com/companies/simantic</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>83 Sciences</t>
+          <t>Locke</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5813,55 +5813,55 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>https://83sciences.ai</t>
+          <t>https://locke.inc</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://83sciences.ai/careers</t>
+          <t>https://locke.inc/careers</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Founding AI Engineer, Head of Sales / Founding GTM, Full-Stack Software Engineer, Work at a Startup</t>
+          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/locke</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLOCKtrack</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>AI-native materials discovery powered by unpublished experimental data</t>
+          <t>AI agents that help companies and governments work together.</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/83-sciences</t>
+          <t>https://www.ycombinator.com/companies/locke</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>WaybillGurugram, HR</t>
+          <t>83 Sciences</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5888,55 +5888,55 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://www.waybill.to</t>
+          <t>https://83sciences.ai</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://www.waybill.to/careers</t>
+          <t>https://83sciences.ai/careers</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding AI Engineer, Head of Sales / Founding GTM, Full-Stack Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/83sciences</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/waybillgurugramhr</t>
+          <t>https://twitter.com/83sciences</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhrinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Managed procurement &amp; inventory for hardware teams.</t>
+          <t>AI-native materials discovery powered by unpublished experimental data</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/waybill</t>
+          <t>https://www.ycombinator.com/companies/83-sciences</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Rational</t>
+          <t>WaybillGurugram, HR</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -5988,45 +5988,45 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://rational.to</t>
+          <t>https://www.waybill.to</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://rational.to/careers</t>
+          <t>https://www.waybill.to/careers</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Forward-Deployed Engineer, Machine Learning Researcher, Software Engineering Intern, Applied AI</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rational</t>
+          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/rational</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rationalinfo</t>
+          <t>https://www.facebook.com/waybillgurugramhrinc</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>AI Employees for In-House Enterprise Accounting</t>
+          <t>Managed procurement &amp; inventory for hardware teams.</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6051,14 +6051,14 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/rational</t>
+          <t>https://www.ycombinator.com/companies/waybill</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://rational.to</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://rational.to/careers</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>Forward-Deployed Engineer, Machine Learning Researcher, Software Engineering Intern, Applied AI</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aktoriaroboticsinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI Employees for In-House Enterprise Accounting</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/rational</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6173,35 +6173,35 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/bloomy</t>
+          <t>https://twitter.com/ooakdata</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bloomy</t>
+          <t>https://www.instagram.com/ooakdata</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>AI-driven 1-to-1 learning for every student</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6263,40 +6263,40 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://ooakdata.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://ooakdata.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/bloomy</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCOOAKtrack</t>
+          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI-driven 1-to-1 learning for every student</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/screenpipe</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6418,7 +6418,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>COACH</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://www.getcoach.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://www.getcoach.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -6461,37 +6461,37 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Brand / Product Designer, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/coach</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgooseinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOACtrack</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>The AI Coach for in person sales reps.</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/ai-coach</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -6533,17 +6533,17 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gutgutgoose</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6646,27 +6646,27 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/synapsesemiconductordurhamnc</t>
+          <t>https://x.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSYNAtrack</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torusapp</t>
+          <t>https://www.facebook.com/torus</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/torus</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/huscarlinc</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6958,7 +6958,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,70 +6968,70 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://aktoria-robotics.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/intelligencefactory</t>
+          <t>https://x.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>https://www.instagram.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KugelAudioBerlin, Berlin, Germany</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7068,35 +7068,35 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinfo</t>
+          <t>https://www.facebook.com/intelligencefactoryinfo</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKUGEtrack</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>KugelAudioBerlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -7177,26 +7177,26 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/klaimee</t>
+          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinc</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7253,35 +7253,35 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/klaimee</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arloindustries</t>
+          <t>https://www.instagram.com/klaimee</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -7357,26 +7357,26 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/astraea</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/astraea</t>
+          <t>https://x.com/arloindustries</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARLOtrack</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -7433,25 +7433,25 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/asendiaai</t>
+          <t>https://twitter.com/astraea</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaaiinfo</t>
+          <t>https://www.facebook.com/astraeainfo</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASTRtrack</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7541,17 +7541,17 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
@@ -7561,17 +7561,17 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/asendiaai</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASENtrack</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,60 +7598,60 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletapp</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7703,17 +7703,17 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7721,27 +7721,27 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/agentphone</t>
+          <t>https://twitter.com/unowallet</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/unowallet</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtime</t>
+          <t>https://www.facebook.com/agentphoneinc</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,55 +7883,55 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/runtime</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/runtime</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/runtime</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCHARtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,55 +7958,55 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arzana</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/arzana</t>
+          <t>https://x.com/characterquilt</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzana</t>
+          <t>https://www.facebook.com/characterquilt</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8063,25 +8063,25 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/manicule</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/manicule</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -8148,45 +8148,45 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arzanaapp</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMANItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,35 +8243,35 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aquashield</t>
+          <t>https://twitter.com/openwork</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/aquashield</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/edenrobotics</t>
+          <t>https://x.com/aquashield</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/aquashield</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAQUAtrack</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,27 +8441,27 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/edenrobotics</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8531,27 +8531,27 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/anoria</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentapp</t>
+          <t>https://www.facebook.com/anoriainfo</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/anoria</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8603,17 +8603,17 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8621,17 +8621,17 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ardent</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -8707,21 +8707,21 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tasklet</t>
+          <t>https://x.com/kuli</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8783,55 +8783,55 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://www.getbiostack.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://www.getbiostack.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Clinical Data Lead, Founding Research Engineer, RL/Reasoning, Work at a Startup</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/biostackplatformsinfo</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aseonlabs</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASEOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,45 +8858,45 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soriaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTASKtrack</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -8977,41 +8977,41 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/ara</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aseonlabsinfo</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>https://www.instagram.com/aseonlabs</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -9048,17 +9048,17 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -9071,22 +9071,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/soria</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minicorinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9143,17 +9143,17 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9161,27 +9161,27 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rivermarkets</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ara</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarkets</t>
+          <t>https://www.facebook.com/araapp</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rivermarkets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,27 +9218,27 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -9247,16 +9247,16 @@
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lumiusdurhamnc</t>
+          <t>https://twitter.com/rivermarkets</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamncinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Adialante</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,27 +9398,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>http://www.adialante.com/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9427,31 +9427,31 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/complir</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/adialante</t>
+          <t>https://www.facebook.com/complirapp</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adialante</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Cancer screening without barriers</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/adialante</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,70 +9488,70 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/biostackplatforms</t>
+          <t>https://x.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatformsapp</t>
+          <t>https://www.facebook.com/lumiusdurhamncinfo</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBIOStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -466,7 +466,7 @@
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="47" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -588,17 +588,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -668,27 +668,27 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>https://www.instagram.com/billiontoone</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tovalainc</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -877,26 +877,26 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/isonohealth</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,60 +938,60 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/deepgram</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/deepgraminc</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/deepgram</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Lattice</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://lattice.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://lattice.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1147,31 +1147,31 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mux</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mux</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mux</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Modern people management platform.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lattice</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1237,41 +1237,41 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>https://www.linkedin.com/company/humaninterest</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/muxinc</t>
+          <t>https://www.facebook.com/humaninterestapp</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/humaninterest</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMUXtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Instawork</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1313,35 +1313,35 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>http://instawork.com</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>http://instawork.com/careers</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>https://www.linkedin.com/company/instawork</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/humaninterest</t>
+          <t>https://x.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINSTtrack</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>A flexible work app that connects businesses with hourly workers.</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/instawork</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Instawork</t>
+          <t>Lattice</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1403,45 +1403,45 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>http://instawork.com</t>
+          <t>https://lattice.com</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>http://instawork.com/careers</t>
+          <t>https://lattice.com/careers</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Senior Account Executive, Staff Software Engineer, Enterprise Account Executive, Head of Data Science / Machine Learning</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/latticeinc</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>A flexible work app that connects businesses with hourly workers.</t>
+          <t>Modern people management platform.</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/instawork</t>
+          <t>https://www.ycombinator.com/companies/lattice</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/xendit</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/xendit</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Shape (ShapeScale)</t>
+          <t>Eight Sleep</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1578,17 +1578,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>https://shapescale.com</t>
+          <t>http://eightsleep.com</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://shapescale.com/careers</t>
+          <t>http://eightsleep.com/careers</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1597,41 +1597,41 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Senior iOS Developer, Work at a Startup</t>
+          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/shapeshapescale</t>
+          <t>https://www.linkedin.com/company/eightsleep</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/shapeshapescale</t>
+          <t>https://twitter.com/eightsleep</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shapeshapescaleinc</t>
+          <t>https://www.facebook.com/eightsleep</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSHAPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
+          <t>The sleep fitness company.</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -1641,14 +1641,14 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
+          <t>https://www.ycombinator.com/companies/eight-sleep</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Shape (ShapeScale)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1668,60 +1668,60 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>https://shapescale.com</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>https://shapescale.com/careers</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
+          <t>Senior iOS Developer, Work at a Startup</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>https://www.linkedin.com/company/shapeshapescale</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circlemedicalinfo</t>
+          <t>https://www.facebook.com/shapeshapescale</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>ShapeScale is a personal 3D scanner and fitness tracker that…</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/shape-shapescale</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Eight Sleep</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>http://eightsleep.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend, Full Stack Engineer - Web Focus, International Paid Media Manager, Director of Business Operations</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinc</t>
+          <t>https://www.facebook.com/circlemedicalapp</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCEIGHtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>The sleep fitness company.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eight-sleep</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GiveCampus</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1848,30 +1848,30 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://go.givecampus.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bitmovininfo</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bitmovin</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBITMtrack</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>The fundraising platform for schools.</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/givecampus</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>GiveCampus</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>http://go.givecampus.com</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>http://go.givecampus.com/careers</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitmovin</t>
+          <t>https://www.linkedin.com/company/givecampus</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/givecampusinc</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>The fundraising platform for schools.</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/givecampus</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/dripcapitalmh</t>
+          <t>https://x.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2151,22 +2151,22 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/vergegenomics</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/vergegenomics</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCVERGtrack</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agilemd</t>
+          <t>https://twitter.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/agilemd</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGILtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachinc</t>
+          <t>https://www.facebook.com/reachinfo</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/branch8</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSNAPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/gemnote</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newstory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCNEWStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2776,22 +2776,22 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ironclad</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ironclad</t>
+          <t>https://twitter.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironcladinfo</t>
+          <t>https://www.facebook.com/ironcladinc</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/luggsaltlakecityut</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutapp</t>
+          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mashgin</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mashgininfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mashgin</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMASHtrack</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/quartzy</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/taraai</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabapp</t>
+          <t>https://www.facebook.com/tabinc</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3316,27 +3316,27 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/streak</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSTREtrack</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/giveffect</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/onesignal</t>
+          <t>https://twitter.com/onesignal</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3586,17 +3586,17 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/magic</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/magic</t>
+          <t>https://x.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/magicinc</t>
+          <t>https://www.facebook.com/magicinfo</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3676,22 +3676,22 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/qventus</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventusinfo</t>
+          <t>https://www.facebook.com/qventusapp</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3766,27 +3766,27 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/hackerrank</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrankinfo</t>
+          <t>https://www.facebook.com/hackerrankinc</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hackerrank</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHACKtrack</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/apollo</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/apollo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/apolloinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/hive</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hive</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/picnicai</t>
+          <t>https://x.com/picnicai</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4098,45 +4098,45 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Kitchener, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Account Development Representative, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/piinpoint</t>
+          <t>https://twitter.com/tempo</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tempoapp</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint helps businesses find the best locations for growth</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4161,14 +4161,14 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/piinpoint</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>PiinPoint</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,55 +4178,55 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Kitchener, Canada</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>https://piinpoint.com</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>https://piinpoint.com/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Account Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/piinpoint</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>PiinPoint helps businesses find the best locations for growth</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/piinpoint</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCNOORtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4396,22 +4396,22 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/cambly</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/cambly</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/cambly</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4486,27 +4486,27 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aptdecoinc</t>
+          <t>https://www.facebook.com/aptdecoapp</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aptdeco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAPTDtrack</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lob</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lobinfo</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lob</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/goldbelly</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsured</t>
+          <t>https://www.facebook.com/simplyinsuredapp</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSIMPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/radar</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5026,27 +5026,27 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/influxdata</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/influxdata</t>
+          <t>https://twitter.com/influxdata</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/influxdata</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINFLtrack</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/etleap</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/padletinfo</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/zentail</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/zentail</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Founding Machine Learning Engineer, Founding Sensing Research Engineer, Founding Wearable Hardware Engineer, Work at a Startup</t>
+          <t>Head of ML, Head of Sensing, Head of Hardware, Work at a Startup</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -5396,17 +5396,17 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thesubvocalcompanyapp</t>
+          <t>https://www.facebook.com/thesubvocalcompanyinfo</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thesubvocalcompany</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTHEStrack</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/covera</t>
+          <t>https://twitter.com/covera</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coverainc</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangelesinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lambdarobotics</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lambdarobotics</t>
+          <t>https://www.facebook.com/lambdaroboticsinc</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5746,17 +5746,17 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/simanticwaterlooon</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterlooonapp</t>
+          <t>https://www.facebook.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/locke</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/locke</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLOCKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/83sciencesapp</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/83sciences</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UC83SCtrack</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/waybillgurugramhrinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/rational</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/rational</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6148,7 +6148,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6173,35 +6173,35 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com</t>
+          <t>https://aktoria.com</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com/careers</t>
+          <t>https://aktoria.com/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
+          <t>Robotics Operations Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>https://www.linkedin.com/company/aktoriarobotics</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ooakdata</t>
+          <t>https://twitter.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooakdata</t>
+          <t>https://www.instagram.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAKTOtrack</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
@@ -6291,17 +6291,17 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/bloomy</t>
+          <t>https://twitter.com/bloomy</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bloomy</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/bloomy</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>AI-driven 1-to-1 learning for every student</t>
+          <t>AI-native learning for every school</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/screenpipe</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/coachapp</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/coach</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCOACtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -6551,17 +6551,17 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,32 +6608,32 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSYNAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/parasma</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/torus</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -6868,7 +6868,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,27 +6878,27 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://ooak-data.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6907,31 +6907,31 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/ooakdata</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarlinc</t>
+          <t>https://www.facebook.com/ooakdata</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,27 +6968,27 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria-robotics.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6997,21 +6997,21 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aktoriarobotics</t>
+          <t>https://twitter.com/huscarl</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
@@ -7058,12 +7058,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7106,17 +7106,17 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINTEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7263,11 +7263,11 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -7281,17 +7281,17 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/klaimeeinc</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arloindustriesinfo</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARLOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASTRtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/asendiaaiinfo</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
@@ -7636,17 +7636,17 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCREVNtrack</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/unowalletinc</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/agentphone</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/runtime</t>
+          <t>https://twitter.com/runtime</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtime</t>
+          <t>https://www.facebook.com/runtimeapp</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -8001,17 +8001,17 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/characterquilt</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -8038,7 +8038,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>Arzana</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8058,17 +8058,17 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://www.arzana.com</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://www.arzana.com/careers</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -8077,11 +8077,11 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/manicule</t>
+          <t>https://www.facebook.com/arzanaapp</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/manicule</t>
+          <t>https://www.instagram.com/arzana</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The autonomous ERP for every manufacturer</t>
         </is>
       </c>
       <c r="Q85" s="4" t="inlineStr">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/arzana</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Arzana</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,55 +8138,55 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.arzana.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/manicule</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzanaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>The autonomous ERP for every manufacturer</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arzana</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
@@ -8266,17 +8266,17 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/openwork</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -8351,37 +8351,37 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aquashield</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/aquashield</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/edenroboticsinc</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aquashield</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAQUAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ardent</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/kuli</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8758,7 +8758,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -8783,45 +8783,45 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.getbiostack.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.getbiostack.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Clinical Data Lead, Founding Research Engineer, RL/Reasoning, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatformsinfo</t>
+          <t>https://www.facebook.com/taskletinfo</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -8873,55 +8873,55 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aseonlabsinc</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTASKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,60 +8948,60 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>https://x.com/soria</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aseonlabsinfo</t>
+          <t>https://www.facebook.com/soriainc</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aseonlabs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,32 +9038,32 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,27 +9071,27 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soria</t>
+          <t>https://x.com/ara</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/araapp</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -9161,22 +9161,22 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/ara</t>
+          <t>https://twitter.com/minicor</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/araapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
@@ -9251,17 +9251,17 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/rivermarkets</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,27 +9308,27 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9337,11 +9337,11 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/rivermarkets</t>
+          <t>https://twitter.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lumiusdurhamncinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="47" customWidth="1" min="12" max="12"/>
+    <col width="43" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,27 +578,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -607,11 +607,11 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -621,27 +621,27 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tovala</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tovalainfo</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/billiontoone</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/billiontooneapp</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,45 +758,45 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>https://www.linkedin.com/company/mason</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/mason</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/isonohealth</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/isonohealthapp</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/deepgram</t>
+          <t>https://x.com/deepgram</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/deepgram</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/soundboks</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soundboksinfo</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/soundboks</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mux</t>
+          <t>https://twitter.com/mux</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/humaninterestapp</t>
+          <t>https://www.facebook.com/humaninterestinc</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINSTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lattice</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/lattice</t>
+          <t>https://twitter.com/lattice</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/latticeinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLATTtrack</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xendit</t>
+          <t>https://www.facebook.com/xenditinc</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/xendit</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/shapeshapescale</t>
+          <t>https://x.com/shapeshapescale</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/shapeshapescale</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, FLORIDA (MD/DO, Board Certified), Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care, Director, Growth Marketing</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/circlemedical</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1876,27 +1876,27 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/bitmovin</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/bitmovin</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bitmovininfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBITMtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1957,11 +1957,11 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior Engineering Manager, Work at a Startup</t>
+          <t>Full Stack Engineer, Senior Engineering Manager, Lead Product Manager, Integrations, Work at a Startup</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/givecampusinc</t>
+          <t>https://www.facebook.com/givecampusapp</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/givecampus</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/vergegenomics</t>
+          <t>https://twitter.com/vergegenomics</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCVERGtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/agilemd</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAGILtrack</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/reachinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREACtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/snapmagic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gemnote</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ironclad</t>
+          <t>https://x.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironcladinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLUGGtrack</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMASHtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/quartzy</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tabinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/streak</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giveffect</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/magic</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/qventus</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventusapp</t>
+          <t>https://www.facebook.com/qventusinc</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCQVENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hackerrankinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHACKtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/picnicaiapp</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/picnicai</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/tempo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempoapp</t>
+          <t>https://www.facebook.com/tempoinc</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/piinpoint</t>
+          <t>https://twitter.com/piinpoint</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/piinpoint</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4293,20 +4293,20 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Lead, Engineer, Lead/Group Product Manager, Chief Technology Officer, Work at a Startup</t>
+          <t>Lead, Engineer, Lead/Group Product Manager, Work at a Startup</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4401,17 +4401,17 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/cambly</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/cambly</t>
+          <t>https://www.facebook.com/camblyapp</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aptdecoapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
@@ -4581,17 +4581,17 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lobinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/goldbelly</t>
+          <t>https://twitter.com/goldbelly</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/goldbellyapp</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGOLDtrack</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4756,22 +4756,22 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/simplyinsured</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsuredapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simplyinsured</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/circuithub</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radarapp</t>
+          <t>https://www.facebook.com/radarinc</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/influxdata</t>
+          <t>https://x.com/influxdata</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCINFLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/etleap</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/padletinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zentail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5386,22 +5386,22 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/thesubvocalcompany</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/thesubvocalcompany</t>
+          <t>https://twitter.com/thesubvocalcompany</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thesubvocalcompanyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/thesubvocalcompany</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coverainc</t>
+          <t>https://www.facebook.com/covera</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCOVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lambdaroboticsinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/locke</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Founding AI Engineer, Head of Sales / Founding GTM, Full-Stack Software Engineer, Work at a Startup</t>
+          <t>Founding AI Engineer, Head of Data Partnerships, Full-Stack Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/83sciences</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/83sciencesapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UC83SCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/rational</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/rational</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCRATItrack</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAKTOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -6238,7 +6238,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6263,55 +6263,55 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/bloomy</t>
+          <t>https://x.com/ooakdata</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bloomy</t>
+          <t>https://www.facebook.com/ooakdatainfo</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bloomy</t>
+          <t>https://www.instagram.com/ooakdata</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCBLOOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>AI-native learning for every school</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -6367,31 +6367,31 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/bloomy</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>Turn your company's computer work into AI agents.</t>
+          <t>AI-native learning for every school</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>COACH</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6443,30 +6443,30 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.getcoach.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Brand / Product Designer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/coach</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/coachapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coach</t>
+          <t>https://www.instagram.com/screenpipe</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>The AI Coach for in person sales reps.</t>
+          <t>Turn your company's computer work into AI agents.</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ai-coach</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,27 +6518,27 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -6551,17 +6551,17 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/synapsesemiconductordurhamnc</t>
+          <t>https://twitter.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,27 +6608,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/synapsesemiconductordurhamncinc</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPARAtrack</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
@@ -6826,22 +6826,22 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/torusapp</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
@@ -6868,7 +6868,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,27 +6878,27 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://ooak-data.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6907,26 +6907,26 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/ooakdata</t>
+          <t>https://twitter.com/huscarl</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -6978,45 +6978,45 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/huscarl</t>
+          <t>https://twitter.com/intelligencefactory</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/intelligencefactoryapp</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>KugelAudioBerlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7068,35 +7068,35 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>KugelAudioBerlin, Berlin, Germany</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -7177,41 +7177,41 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudioberlinberlingermany</t>
+          <t>https://x.com/klaimee</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinc</t>
+          <t>https://www.facebook.com/klaimeeapp</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/klaimee</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKLAItrack</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -7253,40 +7253,40 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/arloindustries</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/klaimeeinc</t>
+          <t>https://www.facebook.com/arloindustriesapp</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCARLOtrack</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,30 +7343,30 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arloindustriesinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7433,25 +7433,25 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -7461,17 +7461,17 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/astraea</t>
+          <t>https://twitter.com/asendiaai</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7541,27 +7541,27 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaaiinfo</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/asendiaai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -7608,17 +7608,17 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -7627,21 +7627,21 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/revnumanchesterengland</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCREVNtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/agentphone</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowalletinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/agentphone</t>
+          <t>https://x.com/runtime</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneinc</t>
+          <t>https://www.facebook.com/runtimeinc</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>https://www.instagram.com/runtime</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,25 +7883,25 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/runtime</t>
+          <t>https://twitter.com/characterquilt</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/characterquilt</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCHARtrack</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/characterquilt</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
@@ -8086,22 +8086,22 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arzana</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/arzana</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arzanaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arzana</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
@@ -8128,7 +8128,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -8257,41 +8257,41 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/edenrobotics</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCEDENtrack</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>AquaShield</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://aquashieldai.com</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://aquashieldai.com/careers</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8351,22 +8351,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/aquashield</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/edenroboticsinc</t>
+          <t>https://www.facebook.com/aquashield</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>AI water leak detection for buildings</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -8391,14 +8391,14 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/aquashield</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>AquaShield</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://aquashieldai.com/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Full-Stack Hardware Engineer, Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>AI water leak detection for buildings</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aquashield</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8531,27 +8531,27 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/anoria</t>
+          <t>https://www.linkedin.com/company/ardent</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ardent</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoriainfo</t>
+          <t>https://www.facebook.com/ardentapp</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anoria</t>
+          <t>https://www.instagram.com/ardent</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8603,17 +8603,17 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8621,27 +8621,27 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/ardent</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/kuliinfo</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/kuli</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -8707,26 +8707,26 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kuli</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>https://twitter.com/tasklet</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tasklet</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8783,55 +8783,55 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taskletinfo</t>
+          <t>https://www.facebook.com/aseonlabsinfo</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCASEOtrack</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,60 +8858,60 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>https://twitter.com/soria</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aseonlabsinc</t>
+          <t>https://www.facebook.com/soria</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/soria</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8958,17 +8958,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -8981,27 +8981,27 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soriainc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -9053,17 +9053,17 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,27 +9071,27 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ara</t>
+          <t>https://x.com/minicor</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/araapp</t>
+          <t>https://www.facebook.com/minicorinfo</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>https://www.instagram.com/minicor</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9143,17 +9143,17 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/rivermarketsinfo</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,70 +9218,70 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://biostack-platforms.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/rivermarkets</t>
+          <t>https://twitter.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/biostackplatforms</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/biostackplatforms</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,60 +9308,60 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/complirinfo</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/complir</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9408,40 +9408,40 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/complir</t>
+          <t>https://x.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>Adialante</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,45 +9488,45 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>http://www.adialante.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>http://www.adialante.com/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Cancer screening without barriers</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/adialante</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="43" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="53" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Tovala</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,70 +578,70 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>http://www.tovala.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainfo</t>
+          <t>https://www.facebook.com/billiontooneapp</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>A smart-oven-paired subscription meal service.</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tovala</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Tovala</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -678,60 +678,60 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.tovala.com</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.tovala.com/careers</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Senior Data Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/tovala</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/billiontoone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontooneapp</t>
+          <t>https://www.facebook.com/tovalainfo</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tovala</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTOVAtrack</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>A smart-oven-paired subscription meal service.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/tovala</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/masoninfo</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mason</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMASOtrack</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -877,26 +877,26 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/isonohealth</t>
+          <t>https://x.com/deepgram</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/isonohealthapp</t>
+          <t>https://www.facebook.com/deepgraminfo</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,14 +921,14 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>SOUNDBOKS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,60 +938,60 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://soundboks.com</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://soundboks.com/careers</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/soundboks</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/deepgram</t>
+          <t>https://twitter.com/soundboks</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soundboksinc</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/soundboks</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>We're creating the loudest battery-driven speaker on the market</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/soundboks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SOUNDBOKS</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1028,70 +1028,70 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://soundboks.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>https://www.linkedin.com/company/isonohealth</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboksinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCISONtrack</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>We're creating the loudest battery-driven speaker on the market</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soundboks</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/mux</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1256,22 +1256,22 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/humaninterestinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/humaninterest</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/instawork</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/instawork</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1426,27 +1426,27 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lattice</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/latticeinc</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lattice</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLATTtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xenditinc</t>
+          <t>https://www.facebook.com/xenditapp</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/eightsleepinfo</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCEIGHtrack</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Circle Medical</t>
+          <t>Bitmovin</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1758,30 +1758,30 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com</t>
+          <t>http://bitmovin.com</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://circlemedical.com/careers</t>
+          <t>http://bitmovin.com/careers</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care, Director, Growth Marketing</t>
+          <t>Sales Director, Work at a Startup</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circlemedicalapp</t>
+          <t>https://www.facebook.com/bitmovin</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Modern primary care via video and in-person</t>
+          <t>Powers OTT online video providers with video developer tools.</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/circle-medical</t>
+          <t>https://www.ycombinator.com/companies/bitmovin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Bitmovin</t>
+          <t>Circle Medical</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1848,50 +1848,50 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com</t>
+          <t>https://circlemedical.com</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>http://bitmovin.com/careers</t>
+          <t>https://circlemedical.com/careers</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Sales Director, Work at a Startup</t>
+          <t>Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care., Primary Care Physician, TEXAS (MD/DO, Board Certified), South Carolina Collaborating / Supervising Physician MD / DO - Telemedicine Primary Care, Director, Insurance Operations</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/bitmovin</t>
+          <t>https://x.com/circlemedical</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/circlemedicalinfo</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/circlemedical</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Powers OTT online video providers with video developer tools.</t>
+          <t>Modern primary care via video and in-person</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bitmovin</t>
+          <t>https://www.ycombinator.com/companies/circle-medical</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/givecampusapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/givecampus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/dripcapitalmh</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vergegenomics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/vergegenomicsinfo</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/agilemd</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAGILtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/reach</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/reach</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/branch8</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/branch8</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/snapmagic</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/snapmagicinfo</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/gemnoteapp</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gemnote</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/newstoryinfo</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ironclad</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ironclad</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I27" s="4" t="n">
@@ -2866,27 +2866,27 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/luggsaltlakecityutinfo</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luggsaltlakecityut</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCLUGGtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mashgin</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCQUARtrack</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,22 +3136,22 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/taraai</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/taraai</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/tab</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTABtrack</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/streak</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCSTREtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGIVEtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/onesignal</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3586,17 +3586,17 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/magicinfo</t>
+          <t>https://www.facebook.com/magicapp</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/qventus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/qventusinc</t>
+          <t>https://www.facebook.com/qventusinfo</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hackerrank</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/hackerrank</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hackerrank</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hive</t>
+          <t>https://twitter.com/hive</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/hiveapp</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hive</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/picnicai</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicaiapp</t>
+          <t>https://www.facebook.com/picnicai</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>PiinPoint</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4098,35 +4098,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Kitchener, Canada</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>https://piinpoint.com</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>https://piinpoint.com/careers</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Account Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>https://www.linkedin.com/company/piinpoint</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tempoinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/piinpoint</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>PiinPoint helps businesses find the best locations for growth</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4161,14 +4161,14 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/piinpoint</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PiinPoint</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,50 +4178,50 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Kitchener, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://piinpoint.com</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://piinpoint.com/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Account Development Representative, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/piinpoint</t>
+          <t>https://twitter.com/tempo</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTEMPtrack</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>PiinPoint helps businesses find the best locations for growth</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/piinpoint</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/camblyapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/aptdeco</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/aptdeco</t>
+          <t>https://twitter.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPTDtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/lob</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lobinfo</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/goldbelly</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCGOLDtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/simplyinsured</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simplyinsuredapp</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCIRCtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/radarinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/radar</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/influxdata</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/etleap</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/padlet</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/padlet</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPADLtrack</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/zentail</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/zentailinc</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/zentail</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5386,17 +5386,17 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/thesubvocalcompany</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/thesubvocalcompany</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/thesubvocalcompanyinfo</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTHEStrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/covera</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5518,7 +5518,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>HemlockLos Angeles</t>
+          <t>Orca Aerospace</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5528,27 +5528,27 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://hemlock.info</t>
+          <t>https://orcaaerospace.com</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://hemlock.info/careers</t>
+          <t>https://orcaaerospace.com/careers</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Software/ML/Signal Processing Engineer, Work at a Startup</t>
+          <t>Founding Flight Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/orcaaerospace</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hemlocklosangeles</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hemlocklosangeles</t>
+          <t>https://www.instagram.com/orcaaerospace</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Force-sensing wristband for training robotic AI</t>
+          <t>AI spacecraft operators that lives onboard the vehicle</t>
         </is>
       </c>
       <c r="Q57" s="4" t="inlineStr">
@@ -5601,14 +5601,14 @@
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/hemlock</t>
+          <t>https://www.ycombinator.com/companies/orca-aerospace</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Lambda Robotics</t>
+          <t>HemlockLos Angeles</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -5628,40 +5628,40 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Los Angeles, CA</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai</t>
+          <t>https://hemlock.info</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://lambdarobotics.ai/careers</t>
+          <t>https://hemlock.info/careers</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
+          <t>Software/ML/Signal Processing Engineer, Contract CAD Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hemlocklosangeles</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lambdarobotics</t>
+          <t>https://x.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>Robotics for AI Infrastructure</t>
+          <t>Force-sensing wristband for training robotic AI</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -5691,14 +5691,14 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
+          <t>https://www.ycombinator.com/companies/hemlock</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SimanticWaterloo, ON</t>
+          <t>Lambda Robotics</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5718,40 +5718,40 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Waterloo, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://simantic.dev</t>
+          <t>https://lambdarobotics.ai</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://simantic.dev/careers</t>
+          <t>https://lambdarobotics.ai/careers</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
+          <t>Mechatronics Engineer, Electrical Engineer, Robotics, Founding Software Engineer, Robotics Infrastructure, Founding GTM</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/simanticwaterlooon</t>
+          <t>https://twitter.com/lambdarobotics</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Firmware simulation for AI agents</t>
+          <t>Robotics for AI Infrastructure</t>
         </is>
       </c>
       <c r="Q59" s="4" t="inlineStr">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/simantic</t>
+          <t>https://www.ycombinator.com/companies/lambda-robotics</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Locke</t>
+          <t>SimanticWaterloo, ON</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -5798,27 +5798,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Waterloo, Canada</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>https://locke.inc</t>
+          <t>https://simantic.dev</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://locke.inc/careers</t>
+          <t>https://simantic.dev/careers</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
+          <t>Lead Simulation Researcher (Electronics / Firmware), Work at a Startup</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/locke</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>AI agents that help companies and governments work together.</t>
+          <t>Firmware simulation for AI agents</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/locke</t>
+          <t>https://www.ycombinator.com/companies/simantic</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>83 Sciences</t>
+          <t>Locke</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://83sciences.ai</t>
+          <t>https://locke.inc</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://83sciences.ai/careers</t>
+          <t>https://locke.inc/careers</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Founding AI Engineer, Head of Data Partnerships, Full-Stack Software Engineer, Work at a Startup</t>
+          <t>Founding Member of Policy Staff, Founding Member of Technical Staff, Work at a Startup</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/83sciences</t>
+          <t>https://twitter.com/locke</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/83sciences</t>
+          <t>https://www.instagram.com/locke</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>AI-native materials discovery powered by unpublished experimental data</t>
+          <t>AI agents that help companies and governments work together.</t>
         </is>
       </c>
       <c r="Q61" s="4" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/83-sciences</t>
+          <t>https://www.ycombinator.com/companies/locke</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>WaybillGurugram, HR</t>
+          <t>83 Sciences</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -5988,40 +5988,40 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://www.waybill.to</t>
+          <t>https://83sciences.ai</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://www.waybill.to/careers</t>
+          <t>https://83sciences.ai/careers</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding AI Engineer, Head of Data Partnerships, Full-Stack Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/83sciences</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/waybillgurugramhr</t>
+          <t>https://x.com/83sciences</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waybillgurugramhr</t>
+          <t>https://www.instagram.com/83sciences</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>Managed procurement &amp; inventory for hardware teams.</t>
+          <t>AI-native materials discovery powered by unpublished experimental data</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -6051,14 +6051,14 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/waybill</t>
+          <t>https://www.ycombinator.com/companies/83-sciences</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Rational</t>
+          <t>WaybillGurugram, HR</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -6078,40 +6078,40 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://rational.to</t>
+          <t>https://www.waybill.to</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://rational.to/careers</t>
+          <t>https://www.waybill.to/careers</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Forward-Deployed Engineer, Machine Learning Researcher, Software Engineering Intern, Applied AI</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/waybillgurugramhr</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCRATItrack</t>
+          <t>https://www.youtube.com/channel/UCWAYBtrack</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>AI Employees for In-House Enterprise Accounting</t>
+          <t>Managed procurement &amp; inventory for hardware teams.</t>
         </is>
       </c>
       <c r="Q63" s="4" t="inlineStr">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/rational</t>
+          <t>https://www.ycombinator.com/companies/waybill</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Rational</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://rational.to</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://rational.to/careers</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -6187,11 +6187,11 @@
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>Forward-Deployed Engineer, Machine Learning Researcher, Software Engineering Intern, Applied AI</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aktoriarobotics</t>
+          <t>https://www.instagram.com/rational</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>AI Employees for In-House Enterprise Accounting</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/rational</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Aktoria Robotics</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://ooakdata.com</t>
+          <t>https://aktoria.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://ooakdata.com/careers</t>
+          <t>https://aktoria.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -6277,31 +6277,31 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
+          <t>Robotics Operations Lead, Work at a Startup</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/ooakdata</t>
+          <t>https://twitter.com/aktoriarobotics</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ooakdatainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>Human as API for robots</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ooakdata</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>AI-native learning for every school</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -6457,16 +6457,16 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/bloomy</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>Turn your company's computer work into AI agents.</t>
+          <t>AI-native learning for every school</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -6547,26 +6547,26 @@
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/gutgutgoose</t>
+          <t>https://www.linkedin.com/company/screenpipe</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/gutgutgoose</t>
+          <t>https://x.com/screenpipe</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/screenpipe</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>Turn your company's computer work into AI agents.</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6608,32 +6608,32 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
@@ -6641,27 +6641,27 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/gutgutgoose</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/synapsesemiconductordurhamncinc</t>
+          <t>https://www.facebook.com/gutgutgooseinfo</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gutgutgoose</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6708,22 +6708,22 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPARAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6803,30 +6803,30 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/parasma</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6836,22 +6836,22 @@
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/torusapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/parasma</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCPARAtrack</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6907,21 +6907,21 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/huscarl</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/torus</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,27 +6968,27 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6997,26 +6997,26 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>https://www.linkedin.com/company/huscarl</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/intelligencefactoryapp</t>
+          <t>https://www.facebook.com/huscarl</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHUSCtrack</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KugelAudioBerlin, Berlin, Germany</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -7068,35 +7068,35 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>KugelAudioBerlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7158,60 +7158,60 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/klaimee</t>
+          <t>https://x.com/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/klaimeeapp</t>
+          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinc</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKLAItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7253,40 +7253,40 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/arloindustriesapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCARLOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,30 +7343,30 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/arloindustries</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -7433,45 +7433,45 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/astraea</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/asendiaai</t>
+          <t>https://x.com/astraea</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/astraeaapp</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7518,17 +7518,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7541,27 +7541,27 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/revnumanchesterengland</t>
+          <t>https://twitter.com/asendiaai</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandinc</t>
+          <t>https://www.facebook.com/asendiaai</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/asendiaai</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -7608,45 +7608,45 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/revnumanchesterenglandapp</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7703,17 +7703,17 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7721,22 +7721,22 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/agentphone</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/unowallet</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/unowallet</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/runtime</t>
+          <t>https://x.com/agentphone</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/runtimeinc</t>
+          <t>https://www.facebook.com/agentphoneinc</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runtime</t>
+          <t>https://www.instagram.com/agentphone</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,35 +7883,35 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/runtime</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/characterquilt</t>
+          <t>https://x.com/runtime</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -7921,17 +7921,17 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/characterquilt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCHARtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/characterquiltapp</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I85" s="4" t="n">
@@ -8128,7 +8128,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -8167,16 +8167,16 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -8186,22 +8186,22 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/maniculeinfo</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>https://www.instagram.com/manicule</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMANItrack</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8243,35 +8243,35 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/edenrobotics</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>https://twitter.com/openwork</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>https://www.instagram.com/openwork</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCEDENtrack</t>
+          <t>https://www.youtube.com/channel/UCOPENtrack</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aquashield</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aquashield</t>
+          <t>https://www.facebook.com/aquashieldinc</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/edenrobotics</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
@@ -8531,27 +8531,27 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ardent</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/ardent</t>
+          <t>https://x.com/anoria</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentapp</t>
+          <t>https://www.facebook.com/anoriainc</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ardent</t>
+          <t>https://www.instagram.com/anoria</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -8631,17 +8631,17 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kuliinfo</t>
+          <t>https://www.facebook.com/ardentinc</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kuli</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8693,40 +8693,40 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tasklet</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tasklet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKULItrack</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Aseon Labs</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8783,40 +8783,40 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com</t>
+          <t>https://www.getbiostack.com</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.aseonlabs.com/careers</t>
+          <t>https://www.getbiostack.com/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
+          <t>Clinical Data Lead, Founding Research Engineer, RL/Reasoning, Work at a Startup</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aseonlabs</t>
+          <t>https://www.linkedin.com/company/biostackplatforms</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aseonlabs</t>
+          <t>https://x.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aseonlabsinfo</t>
+          <t>https://www.facebook.com/biostackplatforms</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCASEOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Robotic pitstops for self-driving cars</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aseon-labs</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,27 +8858,27 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -8887,31 +8887,31 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soria</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soria</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,14 +8931,14 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Aseon Labs</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://www.aseonlabs.com</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://www.aseonlabs.com/careers</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -8977,31 +8977,31 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Senior Robotics Engineer (Full-Time), Founding Mechanical Engineer (Full-Time), Founding Electrical Engineer (Full-Time), Mechanical Engineering Placement (6 Months), New Grad</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>https://www.linkedin.com/company/aseonlabs</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/aseonlabs</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/aseonlabsinfo</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Robotic pitstops for self-driving cars</t>
         </is>
       </c>
       <c r="Q95" s="4" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/aseon-labs</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,27 +9038,27 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -9071,27 +9071,27 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minicorinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minicor</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9143,17 +9143,17 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I97" s="4" t="n">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/rivermarketsinfo</t>
+          <t>https://www.facebook.com/ara</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/ara</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9228,17 +9228,17 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://biostack-platforms.com</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -9247,31 +9247,31 @@
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatforms</t>
+          <t>https://www.facebook.com/minicorapp</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -9337,16 +9337,16 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/complirinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/complir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/complir</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LumiusDurham, NC</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,50 +9398,50 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.lumius-imaging.com/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/lumiusdurhamnc</t>
+          <t>https://twitter.com/complir</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lumiusdurhamnc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/lumius</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Adialante</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9488,45 +9488,45 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>http://www.adialante.com</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>http://www.adialante.com/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Electrical Engineer, Senior Quality Engineer, MRI Tech, Work at a Startup</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -9536,22 +9536,22 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamncapp</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLUMItrack</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Cancer screening without barriers</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="R101" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/adialante</t>
+          <t>https://www.ycombinator.com/companies/lumius</t>
         </is>
       </c>
     </row>

--- a/output/companies.xlsx
+++ b/output/companies.xlsx
@@ -464,9 +464,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="47" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="53" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="47" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BillionToOne</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -578,55 +578,55 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com</t>
+          <t>http://www.bymason.com</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.billiontoone.com/careers</t>
+          <t>http://www.bymason.com/careers</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
+          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/billiontoone</t>
+          <t>https://www.linkedin.com/company/mason</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/mason</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/billiontooneapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>The genetic testing platform detecting and measuring disease.</t>
+          <t>Mason is the fastest way to take smart devices from idea to end user</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/billiontoone</t>
+          <t>https://www.ycombinator.com/companies/mason</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -706,22 +706,22 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/tovala</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tovalainfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tovala</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>BillionToOne</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -758,70 +758,70 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com</t>
+          <t>https://www.billiontoone.com</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>http://www.bymason.com/careers</t>
+          <t>https://www.billiontoone.com/careers</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend, Full Stack Software Engineer, Technical Product Manager, Software, Work at a Startup</t>
+          <t>Senior Software Engineer, Frontend, Senior Software Engineer, Oncology, Senior Software Engineer, Digital Experiences (Prenatal), Senior Software Engineer, Prenatal</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mason</t>
+          <t>https://www.linkedin.com/company/billiontoone</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/billiontoone</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/masoninfo</t>
+          <t>https://www.facebook.com/billiontooneinc</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/billiontoone</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMASOtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mason is the fastest way to take smart devices from idea to end user</t>
+          <t>The genetic testing platform detecting and measuring disease.</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mason</t>
+          <t>https://www.ycombinator.com/companies/billiontoone</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Deepgram</t>
+          <t>iSono Health</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com</t>
+          <t>http://www.isonohealth.com</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>https://www.deepgram.com/careers</t>
+          <t>http://www.isonohealth.com/careers</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -877,26 +877,26 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
+          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepgram</t>
+          <t>https://www.linkedin.com/company/isonohealth</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/deepgram</t>
+          <t>https://twitter.com/isonohealth</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/deepgraminfo</t>
+          <t>https://www.facebook.com/isonohealthapp</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Building foundational AI for speech transcription and understanding.</t>
+          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/deepgram</t>
+          <t>https://www.ycombinator.com/companies/isono-health</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/soundboks</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/soundboksinc</t>
+          <t>https://www.facebook.com/soundboks</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>iSono Health</t>
+          <t>Deepgram</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1043,40 +1043,40 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com</t>
+          <t>https://www.deepgram.com</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>http://www.isonohealth.com/careers</t>
+          <t>https://www.deepgram.com/careers</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Computer Vision/Deep Learning Scientist, Senior Software Engineer - Cloud, Manufacturing Engineer, Work at a Startup</t>
+          <t>Research Scientist, Voice, Sales Development Representative, Corporate Account Executive, Software Engineer - Deepgram for Restaurants</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/isonohealth</t>
+          <t>https://www.linkedin.com/company/deepgram</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/deepgram</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/deepgraminfo</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCISONtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>AI-powered platform for Accessible and Personalized Breast Health…</t>
+          <t>Building foundational AI for speech transcription and understanding.</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1101,14 +1101,14 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/isono-health</t>
+          <t>https://www.ycombinator.com/companies/deepgram</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Human Interest</t>
+          <t>Mux</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com</t>
+          <t>https://www.crunchbase.com/organization/mux-2</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>http://humaninterest.com/careers</t>
+          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Work at a Startup</t>
+          <t>Senior Platform Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/mux</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/mux</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUMAtrack</t>
+          <t>https://www.youtube.com/channel/UCMUXtrack</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>The 401(k) for small and medium-sized businesses.</t>
+          <t>Video infrastructure for developers</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/human-interest</t>
+          <t>https://www.ycombinator.com/companies/mux</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mux</t>
+          <t>Human Interest</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1223,25 +1223,25 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2</t>
+          <t>http://humaninterest.com</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/organization/mux-2/careers</t>
+          <t>http://humaninterest.com/careers</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Work at a Startup</t>
+          <t>Work at a Startup</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/humaninterest</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/humaninterestinc</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Video infrastructure for developers</t>
+          <t>The 401(k) for small and medium-sized businesses.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/mux</t>
+          <t>https://www.ycombinator.com/companies/human-interest</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/instawork</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/instawork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lattice</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/latticeinc</t>
+          <t>https://www.facebook.com/lattice</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1516,22 +1516,22 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/xendit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/xendit</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/xenditapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/xendit</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/eightsleep</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/eightsleepinfo</t>
+          <t>https://www.facebook.com/eightsleep</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCEIGHtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shapeshapescale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/bitmovin</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/bitmovin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBITMtrack</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/circlemedical</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/circlemedical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/circlemedicalinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/givecampus</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/givecampusinfo</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/dripcapitalmh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/dripcapitalmh</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCDRIPtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -2146,17 +2146,17 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/vergegenomics</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/vergegenomics</t>
+          <t>https://x.com/vergegenomics</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/vergegenomicsinfo</t>
+          <t>https://www.facebook.com/vergegenomicsinc</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agilemd</t>
+          <t>https://www.facebook.com/agilemdinc</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/reach</t>
+          <t>https://x.com/reach</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reach</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCREACtrack</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -2416,22 +2416,22 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/branch8</t>
+          <t>https://x.com/branch8</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/branch8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/branch8</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/snapmagic</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/gemnote</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/gemnote</t>
+          <t>https://x.com/gemnote</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gemnoteapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/newstory</t>
+          <t>https://x.com/newstory</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/newstoryinfo</t>
+          <t>https://www.facebook.com/newstory</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ironclad</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/ironclad</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ironclad</t>
+          <t>https://www.facebook.com/ironcladapp</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/luggsaltlakecityutinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/luggsaltlakecityut</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/mashgin</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/mashginapp</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/quartzy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/quartzy</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCQUARtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -3136,27 +3136,27 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/taraai</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/taraai</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taraai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTARAtrack</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3226,27 +3226,27 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tab</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/tab</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/tab</t>
+          <t>https://www.facebook.com/tabinc</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tab</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTABtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
@@ -3316,22 +3316,22 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/streak</t>
+          <t>https://x.com/streak</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/streak</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/streak</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -3406,22 +3406,22 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/giveffect</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/giveffect</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/giveffectapp</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/giveffect</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onesignal</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCONEStrack</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/magic</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/magic</t>
+          <t>https://twitter.com/magic</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/magicapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/magic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCMAGItrack</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/qventus</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/qventus</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/hackerrank</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
@@ -3861,22 +3861,22 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/apollo</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/apolloapp</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/apollo</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCAPOLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -3946,27 +3946,27 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/hive</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hiveapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hive</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHIVEtrack</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/picnicai</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/picnicai</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4088,27 +4088,27 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Kitchener, Canada</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com</t>
+          <t>https://tempo.fit</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://piinpoint.com/careers</t>
+          <t>https://tempo.fit/careers</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -4117,16 +4117,16 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Account Development Representative, Work at a Startup</t>
+          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/piinpoint</t>
+          <t>https://www.linkedin.com/company/tempo</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piinpoint</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>PiinPoint helps businesses find the best locations for growth</t>
+          <t>Live home fitness training powered by computer vision.</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -4161,14 +4161,14 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/piinpoint</t>
+          <t>https://www.ycombinator.com/companies/tempo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>PiinPoint</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4178,50 +4178,50 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Kitchener, Canada</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit</t>
+          <t>https://piinpoint.com</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://tempo.fit/careers</t>
+          <t>https://piinpoint.com/careers</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Sr Computer Vision Engineer, Machine Learning Engineer, Senior Front End Engineer, Work at a Startup</t>
+          <t>Account Development Representative, Work at a Startup</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tempo</t>
+          <t>https://www.linkedin.com/company/piinpoint</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/tempo</t>
+          <t>https://x.com/piinpoint</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCTEMPtrack</t>
+          <t>https://www.youtube.com/channel/UCPIINtrack</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>Live home fitness training powered by computer vision.</t>
+          <t>PiinPoint helps businesses find the best locations for growth</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tempo</t>
+          <t>https://www.ycombinator.com/companies/piinpoint</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4306,22 +4306,22 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/noorahealthtraversecity</t>
+          <t>https://x.com/noorahealthtraversecity</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/noorahealthtraversecityapp</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noorahealthtraversecity</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/cambly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/cambly</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCCAMBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aptdeco</t>
+          <t>https://x.com/aptdeco</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lob</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lobinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/lob</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/goldbelly</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldbellyapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGOLDtrack</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
@@ -4756,22 +4756,22 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/simplyinsured</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/simplyinsuredapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/simplyinsured</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/circuithub</t>
+          <t>https://x.com/circuithub</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/radar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/radar</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -5036,17 +5036,17 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/influxdata</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/influxdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCINFLtrack</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/etleap</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/etleap</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/etleap</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCETLEtrack</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/padlet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/padlet</t>
+          <t>https://www.facebook.com/padletapp</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPADLtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/zentailinc</t>
+          <t>https://www.facebook.com/zentail</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I55" s="4" t="n">
@@ -5391,17 +5391,17 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/thesubvocalcompany</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/thesubvocalcompanyinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thesubvocalcompany</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/covera</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/orcaaerospace</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/hemlocklosangeles</t>
+          <t>https://twitter.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/hemlocklosangeles</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCHEMLtrack</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/lambdarobotics</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/lambdarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/simanticwaterlooon</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/simanticwaterlooon</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/locke</t>
+          <t>https://x.com/locke</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lockeinfo</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCLOCKtrack</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/83sciences</t>
+          <t>https://twitter.com/83sciences</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/83sciences</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/83sciences</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/waybillgurugramhrinc</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/waybillgurugramhr</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCWAYBtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/rational</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/rational</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -6238,7 +6238,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Aktoria Robotics</t>
+          <t>Ooak Data</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria.com</t>
+          <t>https://ooakdata.com</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://aktoria.com/careers</t>
+          <t>https://ooakdata.com/careers</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -6277,26 +6277,26 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Robotics Operations Lead, Work at a Startup</t>
+          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ooakdata</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/aktoriarobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/ooakdata</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>Human as API for robots</t>
+          <t>We turn company data into training data</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/aktoria-robotics</t>
+          <t>https://www.ycombinator.com/companies/ooak-data</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Ooak Data</t>
+          <t>Bloomy</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -6353,30 +6353,30 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com</t>
+          <t>https://bloomylearning.com</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://ooakdata.com/careers</t>
+          <t>https://bloomylearning.com/careers</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>ML engineer, Founding Software Engineer, Founding Data engineer, Founding Marketing Lead</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/bloomyinc</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ooakdata</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>We turn company data into training data</t>
+          <t>AI-native learning for every school</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ooak-data</t>
+          <t>https://www.ycombinator.com/companies/bloomy</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Bloomy</t>
+          <t>screenpipe</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6443,40 +6443,40 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com</t>
+          <t>https://screenpipe.com</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://bloomylearning.com/careers</t>
+          <t>https://screenpipe.com/careers</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bloomy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/screenpipe</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/screenpipe</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>AI-native learning for every school</t>
+          <t>Turn your company's computer work into AI agents.</t>
         </is>
       </c>
       <c r="Q67" s="4" t="inlineStr">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/bloomy</t>
+          <t>https://www.ycombinator.com/companies/screenpipe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>screenpipe</t>
+          <t>Gutgutgoose</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -6533,55 +6533,55 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com</t>
+          <t>https://gutgutgoose.com</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://screenpipe.com/careers</t>
+          <t>https://gutgutgoose.com/careers</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Head of virality, Forward Deployed Engineer (Enterprise), Work at a Startup</t>
+          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/screenpipe</t>
+          <t>https://www.linkedin.com/company/gutgutgoose</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/screenpipe</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/screenpipe</t>
+          <t>https://www.facebook.com/gutgutgoose</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/gutgutgoose</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCGUTGtrack</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>Turn your company's computer work into AI agents.</t>
+          <t>We sequence your gut and build the probiotics it’s missing</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/screenpipe</t>
+          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Gutgutgoose</t>
+          <t>Synapse SemiconductorDurham, NC</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com</t>
+          <t>https://synapsesemi.org</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://gutgutgoose.com/careers</t>
+          <t>https://synapsesemi.org/careers</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I69" s="4" t="n">
@@ -6641,37 +6641,37 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Growth (founding team) — GutGutGoose · San Francisco, in person, Work at a Startup</t>
+          <t>Founding Engineer - RETINA, Work at a Startup</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/gutgutgoose</t>
+          <t>https://twitter.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/gutgutgooseinfo</t>
+          <t>https://www.facebook.com/synapsesemiconductordurhamnc</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gutgutgoose</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCSYNAtrack</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>We sequence your gut and build the probiotics it’s missing</t>
+          <t>New semiconductors that merge compute and vision</t>
         </is>
       </c>
       <c r="Q69" s="4" t="inlineStr">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/gutgutgoose</t>
+          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Synapse SemiconductorDurham, NC</t>
+          <t>Parasma</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6708,22 +6708,22 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Durham, NC</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org</t>
+          <t>https://parasma.com</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://synapsesemi.org/careers</t>
+          <t>https://parasma.com/careers</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer - RETINA, Work at a Startup</t>
+          <t>Founding Scientist, Work at a Startup</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/parasma</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>New semiconductors that merge compute and vision</t>
+          <t>Training human brain cells for AI compute</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/synapse-semiconductor</t>
+          <t>https://www.ycombinator.com/companies/parasma</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Parasma</t>
+          <t>Torus</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6803,55 +6803,55 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com</t>
+          <t>https://www.usetorus.com</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://parasma.com/careers</t>
+          <t>https://www.usetorus.com/careers</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Founding Scientist, Work at a Startup</t>
+          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/parasma</t>
+          <t>https://www.linkedin.com/company/torus</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/torus</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/torus</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/parasma</t>
+          <t>https://www.instagram.com/torus</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCPARAtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Training human brain cells for AI compute</t>
+          <t>Legora for physical engineering firms</t>
         </is>
       </c>
       <c r="Q71" s="4" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/parasma</t>
+          <t>https://www.ycombinator.com/companies/torus</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Torus</t>
+          <t>Huscarl</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com</t>
+          <t>https://www.huscarl.io</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://www.usetorus.com/careers</t>
+          <t>https://www.huscarl.io/careers</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -6907,21 +6907,21 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer (interested in physical infrastructure), Electrical Engineer, Physical Infrastructure Engineer (any discipline), Member of Nontechnical Staff (GTM)</t>
+          <t>Member of technical staff – Paris, Work at a Startup</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/huscarl</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/torus</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>Legora for physical engineering firms</t>
+          <t>AI-native actuary enabling self-insurance for corporations</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/torus</t>
+          <t>https://www.ycombinator.com/companies/huscarl</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Huscarl</t>
+          <t>Intelligence Factory</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -6978,35 +6978,35 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io</t>
+          <t>https://intelligence-factory.com</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.huscarl.io/careers</t>
+          <t>https://intelligence-factory.com/careers</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Member of technical staff – Paris, Work at a Startup</t>
+          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/huscarl</t>
+          <t>https://www.linkedin.com/company/intelligencefactory</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -7016,22 +7016,22 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/huscarl</t>
+          <t>https://www.facebook.com/intelligencefactoryinfo</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/intelligencefactory</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCHUSCtrack</t>
+          <t>https://www.youtube.com/channel/UCINTEtrack</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>AI-native actuary enabling self-insurance for corporations</t>
+          <t>Human Intelligence for Robots</t>
         </is>
       </c>
       <c r="Q73" s="4" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/huscarl</t>
+          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Intelligence Factory</t>
+          <t>KugelAudioBerlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -7068,35 +7068,35 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com</t>
+          <t>https://kugelaudio.com/en</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://intelligence-factory.com/careers</t>
+          <t>https://kugelaudio.com/en/careers</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer: Manipulation, Data Engineer (India), GTM/Operations Intern, Mechanical Engineer (India)</t>
+          <t>Berlin · Part-time · On-site, Work at a Startup</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/intelligencefactory</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/intelligencefactory</t>
+          <t>https://www.instagram.com/kugelaudioberlinberlingermany</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKUGEtrack</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>Human Intelligence for Robots</t>
+          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/intelligence-factory</t>
+          <t>https://www.ycombinator.com/companies/kugelaudio</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>KugelAudioBerlin, Berlin, Germany</t>
+          <t>Klaimee</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7148,60 +7148,60 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en</t>
+          <t>https://www.klaimee.ai</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://kugelaudio.com/en/careers</t>
+          <t>https://www.klaimee.ai/careers</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Berlin · Part-time · On-site, Work at a Startup</t>
+          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kugelaudioberlinberlingermany</t>
+          <t>https://www.linkedin.com/company/klaimee</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/kugelaudioberlinberlingermany</t>
+          <t>https://x.com/klaimee</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kugelaudioberlinberlingermanyinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/klaimee</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Kugel is an on-prem Voice AI model supporting 30+ languages</t>
+          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
         </is>
       </c>
       <c r="Q75" s="4" t="inlineStr">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kugelaudio</t>
+          <t>https://www.ycombinator.com/companies/klaimee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Klaimee</t>
+          <t>Arlo Industries</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai</t>
+          <t>https://arlo1.com</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.klaimee.ai/careers</t>
+          <t>https://arlo1.com/careers</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -7267,16 +7267,16 @@
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>General Counsel &amp; Head of Insurance, Founding GTM Lead, Growth Marketer (Founding), Founding Broker Partnerships Lead</t>
+          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/klaimee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arloindustriesinc</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>Liability insurance for AI Agents. You deploy agents, we cover you.</t>
+          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/klaimee</t>
+          <t>https://www.ycombinator.com/companies/arlo-industries</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Arlo Industries</t>
+          <t>Astraea</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7343,35 +7343,35 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com</t>
+          <t>https://tryastraea.com</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://arlo1.com/careers</t>
+          <t>https://tryastraea.com/careers</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Perception Engineer (Edge CV/AI), Communications &amp; Networking Engineer (Mesh / RF / Edge Systems), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arloindustries</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/astraea</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/astraea</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Track drones and missiles without radars - Accurate, Passive, Scalable</t>
+          <t>AI Operating System for Clinical Development</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/arlo-industries</t>
+          <t>https://www.ycombinator.com/companies/astraea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Astraea</t>
+          <t>Asendia AI</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -7433,45 +7433,45 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com</t>
+          <t>https://asendia.ai</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://tryastraea.com/careers</t>
+          <t>https://asendia.ai/careers</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/astraea</t>
+          <t>https://www.linkedin.com/company/asendiaai</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/astraea</t>
+          <t>https://x.com/asendiaai</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/astraeaapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/astraea</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>AI Operating System for Clinical Development</t>
+          <t>AI recruiters for staffing agencies</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/astraea</t>
+          <t>https://www.ycombinator.com/companies/asendia-ai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Asendia AI</t>
+          <t>RevnuManchester, England</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7518,22 +7518,22 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Manchester, United Kingdom</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai</t>
+          <t>https://revnu.com</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://asendia.ai/careers</t>
+          <t>https://revnu.com/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I79" s="4" t="n">
@@ -7541,27 +7541,27 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer, Marketing Intern - Creative Role, Work at a Startup</t>
+          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/asendiaai</t>
+          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/asendiaai</t>
+          <t>https://x.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/asendiaai</t>
+          <t>https://www.facebook.com/revnumanchesterenglandinfo</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/asendiaai</t>
+          <t>https://www.instagram.com/revnumanchesterengland</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>AI recruiters for staffing agencies</t>
+          <t>The growth infrastructure for the autonomous business</t>
         </is>
       </c>
       <c r="Q79" s="4" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/asendia-ai</t>
+          <t>https://www.ycombinator.com/companies/revnu</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>RevnuManchester, England</t>
+          <t>Uno Wallet</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7608,50 +7608,50 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Manchester, United Kingdom</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com</t>
+          <t>https://myunowallet.com</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://revnu.com/careers</t>
+          <t>https://myunowallet.com/careers</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Founding Associate, Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/revnumanchesterengland</t>
+          <t>https://www.linkedin.com/company/unowallet</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/revnumanchesterengland</t>
+          <t>https://x.com/unowallet</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/revnumanchesterenglandapp</t>
+          <t>https://www.facebook.com/unowalletapp</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/unowallet</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>The growth infrastructure for the autonomous business</t>
+          <t>The AI mobile wallet that replaces Apple Pay</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/revnu</t>
+          <t>https://www.ycombinator.com/companies/uno-wallet</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Uno Wallet</t>
+          <t>AgentPhone</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7703,17 +7703,17 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com</t>
+          <t>https://agentphone.ai</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://myunowallet.com/careers</t>
+          <t>https://agentphone.ai/careers</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I81" s="4" t="n">
@@ -7721,22 +7721,22 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Payment Intelligence, Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/unowallet</t>
+          <t>https://x.com/agentphone</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/unowallet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>The AI mobile wallet that replaces Apple Pay</t>
+          <t>Phone Numbers for AI Agents</t>
         </is>
       </c>
       <c r="Q81" s="4" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/uno-wallet</t>
+          <t>https://www.ycombinator.com/companies/agentphone</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>AgentPhone</t>
+          <t>Runtime</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai</t>
+          <t>https://www.runtm.com</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://agentphone.ai/careers</t>
+          <t>https://www.runtm.com/careers</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -7816,22 +7816,22 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/runtime</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/agentphone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/agentphoneinc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agentphone</t>
+          <t>https://www.instagram.com/runtime</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>Phone Numbers for AI Agents</t>
+          <t>Build and run internal agents, without managing the infrastructure</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/agentphone</t>
+          <t>https://www.ycombinator.com/companies/runtime</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Runtime</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7883,35 +7883,35 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com</t>
+          <t>https://characterquilt.com</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://www.runtm.com/careers</t>
+          <t>https://characterquilt.com/careers</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/runtime</t>
+          <t>https://www.linkedin.com/company/characterquilt</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/runtime</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Build and run internal agents, without managing the infrastructure</t>
+          <t>Computer use agents to deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/runtime</t>
+          <t>https://www.ycombinator.com/companies/characterquilt</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Manicule</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com</t>
+          <t>https://manicule.com</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://characterquilt.com/careers</t>
+          <t>https://manicule.com/careers</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
@@ -7991,22 +7991,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Agent Infrastructure and Reliability, Staff Software Engineer, Agent Infrastructure and Reliability, Member of Technical Staff, Agent Systems, Staff Software Engineer, Agent Systems and Product Quality</t>
+          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/manicule</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/manicule</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/characterquiltapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>Computer use agents to deploy enterprise marketing campaigns</t>
+          <t>AgentRel — Devrel For Agents</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/characterquilt</t>
+          <t>https://www.ycombinator.com/companies/manicule</t>
         </is>
       </c>
     </row>
@@ -8048,12 +8048,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/arzanaapp</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8128,7 +8128,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Manicule</t>
+          <t>OpenWork</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -8153,55 +8153,55 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com</t>
+          <t>https://openworklabs.com</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://manicule.com/careers</t>
+          <t>https://openworklabs.com/careers</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Hiring</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Engineering Intern, Enterprise Sales, X Content Marketer</t>
+          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/manicule</t>
+          <t>https://www.linkedin.com/company/openwork</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/openwork</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/maniculeinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/manicule</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCMANItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>AgentRel — Devrel For Agents</t>
+          <t>The open source alternative to Claude Cowork</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/manicule</t>
+          <t>https://www.ycombinator.com/companies/openwork</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>OpenWork</t>
+          <t>Eden Robotics</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8243,35 +8243,35 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com</t>
+          <t>https://www.edenrobotics.ai</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://openworklabs.com/careers</t>
+          <t>https://www.edenrobotics.ai/careers</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer - SF, Founding Engineer, Work at a Startup</t>
+          <t>Founding Communications Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/openwork</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/openwork</t>
+          <t>https://www.instagram.com/edenrobotics</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCOPENtrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>The open source alternative to Claude Cowork</t>
+          <t>Autonomous services for humanity.</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/openwork</t>
+          <t>https://www.ycombinator.com/companies/eden-robotics</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$12.0M</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -8356,17 +8356,17 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/aquashield</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/aquashield</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aquashieldinc</t>
+          <t>https://www.facebook.com/aquashieldapp</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCAQUAtrack</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Eden Robotics</t>
+          <t>ANORIA</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$115.0M</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai</t>
+          <t>https://www.anoria.com</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.edenrobotics.ai/careers</t>
+          <t>https://www.anoria.com/careers</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I89" s="4" t="n">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Founding Communications Engineer, Work at a Startup</t>
+          <t>Founding Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/anoria</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://twitter.com/edenrobotics</t>
+          <t>https://x.com/anoria</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edenrobotics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>Autonomous services for humanity.</t>
+          <t>The first wearable that reads your emotions to enhance your EQ.</t>
         </is>
       </c>
       <c r="Q89" s="4" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/eden-robotics</t>
+          <t>https://www.ycombinator.com/companies/anoria</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>ANORIA</t>
+          <t>BioStack Platforms</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com</t>
+          <t>https://www.getbiostack.com</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://www.anoria.com/careers</t>
+          <t>https://www.getbiostack.com/careers</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Founding Software Engineer, Work at a Startup</t>
+          <t>Clinical Data Lead, Founding Research Engineer, RL/Reasoning, Work at a Startup</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -8541,27 +8541,27 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>https://x.com/anoria</t>
+          <t>https://x.com/biostackplatforms</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/anoriainc</t>
+          <t>https://www.facebook.com/biostackplatformsinc</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anoria</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCBIOStrack</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>The first wearable that reads your emotions to enhance your EQ.</t>
+          <t>Real world training envs for healthcare AI models</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/anoria</t>
+          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Ardent</t>
+          <t>Kuli</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8603,17 +8603,17 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com</t>
+          <t>https://kuli.one</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://tryardent.com/careers</t>
+          <t>https://kuli.one/careers</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Hiring</t>
         </is>
       </c>
       <c r="I91" s="4" t="n">
@@ -8621,22 +8621,22 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/kuli</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/kuli</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ardentinc</t>
+          <t>https://www.facebook.com/kuliapp</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCKULItrack</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Database sandboxes for Agents</t>
+          <t>AI coworker for marketing teams at the largest consumer brands</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ardent</t>
+          <t>https://www.ycombinator.com/companies/kuli</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Kuli</t>
+          <t>Ardent</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>$12.0M</t>
+          <t>$24.5M</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one</t>
+          <t>https://tryardent.com</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://kuli.one/careers</t>
+          <t>https://tryardent.com/careers</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Founding Engineer - Product (Staff), Work at a Startup</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/kuli</t>
+          <t>https://twitter.com/ardent</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKULItrack</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>AI coworker for marketing teams at the largest consumer brands</t>
+          <t>Database sandboxes for Agents</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/kuli</t>
+          <t>https://www.ycombinator.com/companies/ardent</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>BioStack Platforms</t>
+          <t>Tasklet</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>$115.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8783,55 +8783,55 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://www.getbiostack.com</t>
+          <t>https://tasklet.ai</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.getbiostack.com/careers</t>
+          <t>https://tasklet.ai/careers</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Clinical Data Lead, Founding Research Engineer, RL/Reasoning, Work at a Startup</t>
+          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Customer Success Engineer</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biostackplatforms</t>
+          <t>https://www.linkedin.com/company/tasklet</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://x.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/biostackplatforms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/tasklet</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCTASKtrack</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Real world training envs for healthcare AI models</t>
+          <t>Agents that own the work</t>
         </is>
       </c>
       <c r="Q93" s="4" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/biostack-platforms</t>
+          <t>https://www.ycombinator.com/companies/tasklet-2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Tasklet</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -8858,45 +8858,45 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai</t>
+          <t>https://www.soriaanalytics.com</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://tasklet.ai/careers</t>
+          <t>https://www.soriaanalytics.com/careers</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Head of Design Engineering, Software Engineer — AI Infra, Software Engineer — Platform, Sales Executive</t>
+          <t>Founding Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tasklet</t>
+          <t>https://www.linkedin.com/company/soria</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/soriaapp</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tasklet</t>
+          <t>https://www.instagram.com/soria</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>Agents that own the work</t>
+          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/tasklet-2</t>
+          <t>https://www.ycombinator.com/companies/soria</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>$5.2M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/aseonlabsinfo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.instagram.com/aseonlabs</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
@@ -9028,7 +9028,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Ara</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9038,32 +9038,32 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com</t>
+          <t>https://ara.so</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://www.soriaanalytics.com/careers</t>
+          <t>https://ara.so/careers</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Founding Engineer, Work at a Startup</t>
+          <t>Engineering Internship, Work at a Startup</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/ara</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>AI Financial Research Terminal built for Healthcare (and beyond)</t>
+          <t>The Cloud Coding Agent</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/soria</t>
+          <t>https://www.ycombinator.com/companies/ara</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Ara</t>
+          <t>Minicor</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so</t>
+          <t>https://minicor.com</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://ara.so/careers</t>
+          <t>https://minicor.com/careers</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -9161,27 +9161,27 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>Engineering Internship, Work at a Startup</t>
+          <t>Software Engineer, Work at a Startup</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ara</t>
+          <t>https://www.linkedin.com/company/minicor</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://twitter.com/minicor</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/ara</t>
+          <t>https://www.facebook.com/minicorinfo</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ara</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>The Cloud Coding Agent</t>
+          <t>Scalable windows desktop automations</t>
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ara</t>
+          <t>https://www.ycombinator.com/companies/minicor</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Minicor</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$5.2M</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com</t>
+          <t>https://www.rivermarkets.com</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://minicor.com/careers</t>
+          <t>https://www.rivermarkets.com/careers</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Work at a Startup</t>
+          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/rivermarkets</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minicorapp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>Scalable windows desktop automations</t>
+          <t>Prime brokerage for prediction markets</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -9291,14 +9291,14 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/minicor</t>
+          <t>https://www.ycombinator.com/companies/river-markets</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>Complir</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9308,55 +9308,55 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>$24.5M</t>
+          <t>$8.4M</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>Series A</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com</t>
+          <t>https://complir.io</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.rivermarkets.com/careers</t>
+          <t>https://complir.io/careers</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Not Hiring</t>
+          <t>Hiring</t>
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Founding Engineer - River Markets (YC P26), Work at a Startup</t>
+          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.linkedin.com/company/complir</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://x.com/complir</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/complirapp</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.youtube.com/channel/UCCOMPtrack</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Prime brokerage for prediction markets</t>
+          <t>Vanta for physical products</t>
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr">
@@ -9381,14 +9381,14 @@
       </c>
       <c r="R99" s="4" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/river-markets</t>
+          <t>https://www.ycombinator.com/companies/complir</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Complir</t>
+          <t>LumiusDurham, NC</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9398,27 +9398,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>$8.4M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Series A</t>
+          <t>Series B</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Durham, NC</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io</t>
+          <t>https://www.lumius-imaging.com</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://complir.io/careers</t>
+          <t>https://www.lumius-imaging.com/careers</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9427,26 +9427,26 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Head of Germany, Backend Engineer, Fullstack Engineer, Head of UK</t>
+          <t>Founding Hardware Engineer - ASICs &amp; Embedded Systems, Work at a Startup</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/complir</t>
+          <t>https://www.linkedin.com/company/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>https://twitter.com/complir</t>
+          <t>https://x.com/lumiusdurhamnc</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://www.facebook.com/lumiusdurhamncinc</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>Vanta for physical products</t>
+          <t>Fast, smart, accessible 3D ultrasound that anyone can use</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineS